--- a/resource/Script/script_SuspiciousClock.xlsx
+++ b/resource/Script/script_SuspiciousClock.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\usosctheater\resource\Script\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EDEAF3D-D15F-4750-AC67-FF587341F7D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF2607B0-7198-4430-BB37-387193F83E2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{EADB399D-2B1E-4E96-B3F6-5A929A7D9084}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="335">
   <si>
     <t>Type</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -138,10 +138,6 @@
     <t>2</t>
   </si>
   <si>
-    <t>일상?</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>오하요쓰</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -650,14 +646,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>clock.img</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>물건 꺼내는 효과음</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>smile2</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -702,10 +690,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>변신 효과음</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>clean</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -891,6 +875,380 @@
   </si>
   <si>
     <t>smile2 face_rebellion1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>se_oku</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>stopwatch.img</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>se_botan</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SCS001001</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SCS001002</t>
+  </si>
+  <si>
+    <t>SCS001003</t>
+  </si>
+  <si>
+    <t>SCS001004</t>
+  </si>
+  <si>
+    <t>SCS001005</t>
+  </si>
+  <si>
+    <t>SCS001006</t>
+  </si>
+  <si>
+    <t>SCS001007</t>
+  </si>
+  <si>
+    <t>SCS001008</t>
+  </si>
+  <si>
+    <t>SCS001009</t>
+  </si>
+  <si>
+    <t>SCS001010</t>
+  </si>
+  <si>
+    <t>SCS001011</t>
+  </si>
+  <si>
+    <t>SCS001012</t>
+  </si>
+  <si>
+    <t>SCS001013</t>
+  </si>
+  <si>
+    <t>SCS001014</t>
+  </si>
+  <si>
+    <t>SCS001015</t>
+  </si>
+  <si>
+    <t>SCS001016</t>
+  </si>
+  <si>
+    <t>SCS001017</t>
+  </si>
+  <si>
+    <t>SCS001018</t>
+  </si>
+  <si>
+    <t>SCS001019</t>
+  </si>
+  <si>
+    <t>SCS001020</t>
+  </si>
+  <si>
+    <t>SCS001021</t>
+  </si>
+  <si>
+    <t>SCS001022</t>
+  </si>
+  <si>
+    <t>SCS001023</t>
+  </si>
+  <si>
+    <t>SCS001024</t>
+  </si>
+  <si>
+    <t>SCS001025</t>
+  </si>
+  <si>
+    <t>SCS001026</t>
+  </si>
+  <si>
+    <t>SCS001027</t>
+  </si>
+  <si>
+    <t>SCS001028</t>
+  </si>
+  <si>
+    <t>SCS001029</t>
+  </si>
+  <si>
+    <t>SCS001030</t>
+  </si>
+  <si>
+    <t>SCS001031</t>
+  </si>
+  <si>
+    <t>SCS001032</t>
+  </si>
+  <si>
+    <t>SCS001033</t>
+  </si>
+  <si>
+    <t>SCS001034</t>
+  </si>
+  <si>
+    <t>SCS001035</t>
+  </si>
+  <si>
+    <t>SCS001036</t>
+  </si>
+  <si>
+    <t>SCS001037</t>
+  </si>
+  <si>
+    <t>SCS001038</t>
+  </si>
+  <si>
+    <t>SCS001039</t>
+  </si>
+  <si>
+    <t>SCS001040</t>
+  </si>
+  <si>
+    <t>SCS001041</t>
+  </si>
+  <si>
+    <t>SCS001042</t>
+  </si>
+  <si>
+    <t>SCS001043</t>
+  </si>
+  <si>
+    <t>SCS001044</t>
+  </si>
+  <si>
+    <t>SCS001045</t>
+  </si>
+  <si>
+    <t>SCS001046</t>
+  </si>
+  <si>
+    <t>SCS001047</t>
+  </si>
+  <si>
+    <t>SCS001048</t>
+  </si>
+  <si>
+    <t>SCS001049</t>
+  </si>
+  <si>
+    <t>SCS001050</t>
+  </si>
+  <si>
+    <t>SCS001051</t>
+  </si>
+  <si>
+    <t>SCS001052</t>
+  </si>
+  <si>
+    <t>SCS001053</t>
+  </si>
+  <si>
+    <t>SCS001054</t>
+  </si>
+  <si>
+    <t>SCS001055</t>
+  </si>
+  <si>
+    <t>SCS001056</t>
+  </si>
+  <si>
+    <t>SCS001057</t>
+  </si>
+  <si>
+    <t>SCS001058</t>
+  </si>
+  <si>
+    <t>SCS001059</t>
+  </si>
+  <si>
+    <t>SCS001060</t>
+  </si>
+  <si>
+    <t>SCS001061</t>
+  </si>
+  <si>
+    <t>SCS001062</t>
+  </si>
+  <si>
+    <t>SCS001063</t>
+  </si>
+  <si>
+    <t>SCS001064</t>
+  </si>
+  <si>
+    <t>SCS001065</t>
+  </si>
+  <si>
+    <t>SCS001066</t>
+  </si>
+  <si>
+    <t>SCS001067</t>
+  </si>
+  <si>
+    <t>SCS001068</t>
+  </si>
+  <si>
+    <t>SCS001069</t>
+  </si>
+  <si>
+    <t>SCS001070</t>
+  </si>
+  <si>
+    <t>SCS001071</t>
+  </si>
+  <si>
+    <t>SCS001072</t>
+  </si>
+  <si>
+    <t>SCS001073</t>
+  </si>
+  <si>
+    <t>SCS001074</t>
+  </si>
+  <si>
+    <t>SCS001075</t>
+  </si>
+  <si>
+    <t>SCS001076</t>
+  </si>
+  <si>
+    <t>SCS001077</t>
+  </si>
+  <si>
+    <t>SCS001078</t>
+  </si>
+  <si>
+    <t>SCS001079</t>
+  </si>
+  <si>
+    <t>SCS001080</t>
+  </si>
+  <si>
+    <t>SCS001081</t>
+  </si>
+  <si>
+    <t>SCS001082</t>
+  </si>
+  <si>
+    <t>SCS001083</t>
+  </si>
+  <si>
+    <t>SCS001084</t>
+  </si>
+  <si>
+    <t>SCS001085</t>
+  </si>
+  <si>
+    <t>SCS001086</t>
+  </si>
+  <si>
+    <t>SCS001087</t>
+  </si>
+  <si>
+    <t>SCS001088</t>
+  </si>
+  <si>
+    <t>SCS001089</t>
+  </si>
+  <si>
+    <t>SCS001090</t>
+  </si>
+  <si>
+    <t>SCS001091</t>
+  </si>
+  <si>
+    <t>SCS001092</t>
+  </si>
+  <si>
+    <t>SCS001093</t>
+  </si>
+  <si>
+    <t>SCS001094</t>
+  </si>
+  <si>
+    <t>SCS001095</t>
+  </si>
+  <si>
+    <t>SCS001096</t>
+  </si>
+  <si>
+    <t>SCS001097</t>
+  </si>
+  <si>
+    <t>SCS001098</t>
+  </si>
+  <si>
+    <t>SCS001099</t>
+  </si>
+  <si>
+    <t>SCS001100</t>
+  </si>
+  <si>
+    <t>SCS001101</t>
+  </si>
+  <si>
+    <t>SCS001102</t>
+  </si>
+  <si>
+    <t>SCS001103</t>
+  </si>
+  <si>
+    <t>SCS001104</t>
+  </si>
+  <si>
+    <t>SCS001105</t>
+  </si>
+  <si>
+    <t>SCS001106</t>
+  </si>
+  <si>
+    <t>SCS001107</t>
+  </si>
+  <si>
+    <t>SCS001108</t>
+  </si>
+  <si>
+    <t>SCS001109</t>
+  </si>
+  <si>
+    <t>SCS001110</t>
+  </si>
+  <si>
+    <t>SCS001111</t>
+  </si>
+  <si>
+    <t>SCS001112</t>
+  </si>
+  <si>
+    <t>SCS001113</t>
+  </si>
+  <si>
+    <t>SCS001114</t>
+  </si>
+  <si>
+    <t>SCS001115</t>
+  </si>
+  <si>
+    <t>0.4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BGM_2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BGM_10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BGM_12</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -940,7 +1298,7 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -956,12 +1314,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -986,7 +1338,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1008,16 +1360,13 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="2" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1283,8 +1632,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1B221B17-DBD4-4E16-9869-7F66B6AFF02D}" name="표1" displayName="표1" ref="B2:P157" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15" headerRowCellStyle="HeadLine">
-  <autoFilter ref="B2:P157" xr:uid="{160FF696-8FC2-44DF-96A2-501D4731471F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1B221B17-DBD4-4E16-9869-7F66B6AFF02D}" name="표1" displayName="표1" ref="B2:P163" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15" headerRowCellStyle="HeadLine">
+  <autoFilter ref="B2:P163" xr:uid="{160FF696-8FC2-44DF-96A2-501D4731471F}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{81072C37-B109-45F0-B145-C9B738FEFBF4}" name="Type" dataDxfId="14"/>
     <tableColumn id="2" xr3:uid="{CD1928B4-F262-497E-9ECE-D09B04C8F366}" name="Name" dataDxfId="13"/>
@@ -1603,7 +1952,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C26F6916-30D7-453E-B293-0D9DCEC01355}">
-  <dimension ref="A2:P157"/>
+  <dimension ref="A2:P163"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.796875" style="2"/>
@@ -1691,11 +2040,11 @@
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
       <c r="P3" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="9"/>
+      <c r="A4" s="3"/>
       <c r="B4" s="4" t="s">
         <v>16</v>
       </c>
@@ -1712,7 +2061,7 @@
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4" t="s">
-        <v>27</v>
+        <v>332</v>
       </c>
       <c r="N4" s="4" t="s">
         <v>18</v>
@@ -1750,17 +2099,19 @@
         <v>24</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="5"/>
+        <v>27</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>216</v>
+      </c>
       <c r="F6" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>136</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>137</v>
       </c>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
@@ -1781,9 +2132,11 @@
         <v>25</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="5"/>
+        <v>28</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>217</v>
+      </c>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
@@ -1806,23 +2159,25 @@
         <v>24</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" s="4"/>
+        <v>29</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>218</v>
+      </c>
       <c r="F8" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
       <c r="L8" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
@@ -1837,9 +2192,11 @@
         <v>25</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="5"/>
+        <v>30</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>219</v>
+      </c>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
@@ -1862,9 +2219,11 @@
         <v>25</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" s="5"/>
+        <v>31</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>220</v>
+      </c>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
@@ -1887,23 +2246,25 @@
         <v>24</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" s="4"/>
+        <v>32</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>221</v>
+      </c>
       <c r="F11" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
       <c r="L11" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M11" s="4"/>
       <c r="N11" s="4"/>
@@ -1912,24 +2273,24 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B12" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C12" s="5"/>
-      <c r="D12" s="7"/>
+      <c r="D12" s="4"/>
       <c r="E12" s="8"/>
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
-      <c r="I12" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
-      <c r="O12" s="7"/>
-      <c r="P12" s="7"/>
+      <c r="I12" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
+      <c r="N12" s="4"/>
+      <c r="O12" s="4"/>
+      <c r="P12" s="4"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B13" s="4" t="s">
@@ -1937,17 +2298,17 @@
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
+      <c r="E13" s="8"/>
       <c r="F13" s="4"/>
       <c r="G13" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H13" s="4"/>
       <c r="I13" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1955,16 +2316,16 @@
       <c r="N13" s="4"/>
       <c r="O13" s="4"/>
       <c r="P13" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B14" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
+      <c r="E14" s="8"/>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
@@ -1975,7 +2336,7 @@
       </c>
       <c r="L14" s="6"/>
       <c r="M14" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N14" s="6" t="s">
         <v>23</v>
@@ -1985,16 +2346,16 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B15" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
+      <c r="E15" s="8"/>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
       <c r="I15" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J15" s="6"/>
       <c r="K15" s="6"/>
@@ -2012,23 +2373,25 @@
         <v>24</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="E16" s="4"/>
+        <v>152</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>222</v>
+      </c>
       <c r="F16" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>22</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
       <c r="L16" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M16" s="4"/>
       <c r="N16" s="4"/>
@@ -2043,9 +2406,11 @@
         <v>24</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E17" s="4"/>
+        <v>33</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>223</v>
+      </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
@@ -2053,7 +2418,7 @@
       <c r="J17" s="4"/>
       <c r="K17" s="4"/>
       <c r="L17" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M17" s="4"/>
       <c r="N17" s="4"/>
@@ -2061,13 +2426,13 @@
       <c r="P17" s="4"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" s="9"/>
+      <c r="A18" s="3"/>
       <c r="B18" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
+      <c r="E18" s="8"/>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
@@ -2079,17 +2444,17 @@
       <c r="N18" s="4"/>
       <c r="O18" s="4"/>
       <c r="P18" s="4" t="s">
-        <v>156</v>
+        <v>214</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" s="9"/>
+      <c r="A19" s="3"/>
       <c r="B19" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
+      <c r="E19" s="8"/>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
@@ -2100,7 +2465,7 @@
       </c>
       <c r="L19" s="6"/>
       <c r="M19" s="6" t="s">
-        <v>157</v>
+        <v>213</v>
       </c>
       <c r="N19" s="6" t="s">
         <v>23</v>
@@ -2110,16 +2475,16 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B20" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
+      <c r="E20" s="8"/>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
       <c r="I20" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J20" s="6"/>
       <c r="K20" s="6"/>
@@ -2137,9 +2502,11 @@
         <v>25</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E21" s="5"/>
+        <v>34</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>224</v>
+      </c>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
@@ -2162,9 +2529,11 @@
         <v>25</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E22" s="5"/>
+        <v>35</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>225</v>
+      </c>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
@@ -2187,23 +2556,25 @@
         <v>24</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E23" s="4"/>
+        <v>36</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>226</v>
+      </c>
       <c r="F23" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>22</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
       <c r="L23" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M23" s="4"/>
       <c r="N23" s="4"/>
@@ -2218,9 +2589,11 @@
         <v>25</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E24" s="5"/>
+        <v>37</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
       <c r="H24" s="5"/>
@@ -2243,23 +2616,25 @@
         <v>24</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E25" s="4"/>
+        <v>38</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>228</v>
+      </c>
       <c r="F25" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>22</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
       <c r="K25" s="4"/>
       <c r="L25" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M25" s="4"/>
       <c r="N25" s="4"/>
@@ -2274,9 +2649,11 @@
         <v>25</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E26" s="5"/>
+        <v>39</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>229</v>
+      </c>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
       <c r="H26" s="5"/>
@@ -2299,23 +2676,25 @@
         <v>24</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E27" s="4"/>
+        <v>40</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>230</v>
+      </c>
       <c r="F27" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G27" s="5" t="s">
         <v>22</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
       <c r="K27" s="4"/>
       <c r="L27" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M27" s="4"/>
       <c r="N27" s="4"/>
@@ -2330,9 +2709,11 @@
         <v>25</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E28" s="5"/>
+        <v>41</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>231</v>
+      </c>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
@@ -2355,23 +2736,25 @@
         <v>24</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E29" s="4"/>
+        <v>42</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>232</v>
+      </c>
       <c r="F29" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G29" s="5" t="s">
         <v>22</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="I29" s="4"/>
       <c r="J29" s="4"/>
       <c r="K29" s="4"/>
       <c r="L29" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M29" s="4"/>
       <c r="N29" s="4"/>
@@ -2386,23 +2769,25 @@
         <v>24</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E30" s="4"/>
+        <v>43</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>233</v>
+      </c>
       <c r="F30" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G30" s="5" t="s">
         <v>22</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
       <c r="K30" s="4"/>
       <c r="L30" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M30" s="4"/>
       <c r="N30" s="4"/>
@@ -2417,9 +2802,11 @@
         <v>25</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E31" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>234</v>
+      </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
@@ -2442,9 +2829,11 @@
         <v>25</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E32" s="5"/>
+        <v>45</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>235</v>
+      </c>
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
       <c r="H32" s="5"/>
@@ -2461,24 +2850,24 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B33" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C33" s="5"/>
-      <c r="D33" s="7"/>
+      <c r="D33" s="4"/>
       <c r="E33" s="8"/>
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
       <c r="H33" s="5"/>
-      <c r="I33" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="J33" s="7"/>
-      <c r="K33" s="7"/>
-      <c r="L33" s="7"/>
-      <c r="M33" s="7"/>
-      <c r="N33" s="7"/>
-      <c r="O33" s="7"/>
-      <c r="P33" s="7"/>
+      <c r="I33" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="4"/>
+      <c r="N33" s="4"/>
+      <c r="O33" s="4"/>
+      <c r="P33" s="4"/>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B34" s="4" t="s">
@@ -2486,17 +2875,17 @@
       </c>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
+      <c r="E34" s="8"/>
       <c r="F34" s="4"/>
       <c r="G34" s="4" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="H34" s="4"/>
       <c r="I34" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -2504,16 +2893,16 @@
       <c r="N34" s="4"/>
       <c r="O34" s="4"/>
       <c r="P34" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B35" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C35" s="6"/>
       <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
+      <c r="E35" s="8"/>
       <c r="F35" s="6"/>
       <c r="G35" s="6"/>
       <c r="H35" s="6"/>
@@ -2522,7 +2911,7 @@
       <c r="K35" s="6"/>
       <c r="L35" s="6"/>
       <c r="M35" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="N35" s="6"/>
       <c r="O35" s="6"/>
@@ -2533,26 +2922,28 @@
         <v>21</v>
       </c>
       <c r="C36" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D36" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D36" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E36" s="4"/>
+      <c r="E36" s="8" t="s">
+        <v>236</v>
+      </c>
       <c r="F36" s="5" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
       <c r="K36" s="4"/>
       <c r="L36" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M36" s="4"/>
       <c r="N36" s="4"/>
@@ -2561,18 +2952,18 @@
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B37" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C37" s="6"/>
       <c r="D37" s="6"/>
-      <c r="E37" s="6"/>
+      <c r="E37" s="8"/>
       <c r="F37" s="6"/>
       <c r="G37" s="6"/>
       <c r="H37" s="6"/>
       <c r="I37" s="6"/>
       <c r="J37" s="6"/>
       <c r="K37" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="L37" s="6"/>
       <c r="M37" s="6"/>
@@ -2588,23 +2979,25 @@
         <v>24</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E38" s="4"/>
+        <v>48</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>237</v>
+      </c>
       <c r="F38" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G38" s="5" t="s">
         <v>22</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I38" s="4"/>
       <c r="J38" s="4"/>
       <c r="K38" s="4"/>
       <c r="L38" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M38" s="4"/>
       <c r="N38" s="4"/>
@@ -2616,26 +3009,28 @@
         <v>21</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E39" s="4"/>
+        <v>49</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>238</v>
+      </c>
       <c r="F39" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="H39" s="5" t="s">
         <v>165</v>
-      </c>
-      <c r="G39" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="H39" s="5" t="s">
-        <v>168</v>
       </c>
       <c r="I39" s="4"/>
       <c r="J39" s="4"/>
       <c r="K39" s="4"/>
       <c r="L39" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M39" s="4"/>
       <c r="N39" s="4"/>
@@ -2643,13 +3038,13 @@
       <c r="P39" s="4"/>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A40" s="9"/>
+      <c r="A40" s="3"/>
       <c r="B40" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
+      <c r="E40" s="8"/>
       <c r="F40" s="4"/>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
@@ -2661,17 +3056,17 @@
       <c r="N40" s="4"/>
       <c r="O40" s="4"/>
       <c r="P40" s="4" t="s">
-        <v>156</v>
+        <v>214</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A41" s="10"/>
+      <c r="A41" s="7"/>
       <c r="B41" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C41" s="6"/>
       <c r="D41" s="6"/>
-      <c r="E41" s="6"/>
+      <c r="E41" s="8"/>
       <c r="F41" s="6"/>
       <c r="G41" s="6"/>
       <c r="H41" s="6"/>
@@ -2682,7 +3077,7 @@
       </c>
       <c r="L41" s="6"/>
       <c r="M41" s="6" t="s">
-        <v>169</v>
+        <v>215</v>
       </c>
       <c r="N41" s="6" t="s">
         <v>23</v>
@@ -2693,29 +3088,29 @@
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42"/>
       <c r="B42" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C42" s="5"/>
-      <c r="D42" s="7"/>
+      <c r="D42" s="4"/>
       <c r="E42" s="8"/>
       <c r="F42" s="5"/>
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
-      <c r="I42" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="J42" s="7"/>
-      <c r="K42" s="7"/>
-      <c r="L42" s="7"/>
-      <c r="M42" s="7"/>
-      <c r="N42" s="7"/>
-      <c r="O42" s="7"/>
-      <c r="P42" s="7"/>
+      <c r="I42" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="J42" s="4"/>
+      <c r="K42" s="4"/>
+      <c r="L42" s="4"/>
+      <c r="M42" s="4"/>
+      <c r="N42" s="4"/>
+      <c r="O42" s="4"/>
+      <c r="P42" s="4"/>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43"/>
       <c r="B43" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
@@ -2724,121 +3119,120 @@
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
       <c r="I43" s="4"/>
-      <c r="J43" s="4"/>
+      <c r="J43" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
-      <c r="M43" s="4"/>
-      <c r="N43" s="4"/>
+      <c r="M43" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="N43" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="O43" s="4"/>
-      <c r="P43" s="4" t="s">
-        <v>143</v>
-      </c>
+      <c r="P43" s="4"/>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44"/>
-      <c r="B44" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="6"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="6"/>
-      <c r="I44" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="J44" s="6"/>
-      <c r="K44" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="L44" s="6"/>
-      <c r="M44" s="6"/>
-      <c r="N44" s="6"/>
-      <c r="O44" s="6"/>
-      <c r="P44" s="6"/>
+      <c r="B44" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="4"/>
+      <c r="L44" s="4"/>
+      <c r="M44" s="4"/>
+      <c r="N44" s="4"/>
+      <c r="O44" s="4"/>
+      <c r="P44" s="4" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45"/>
       <c r="B45" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C45" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="8"/>
+      <c r="F45" s="6"/>
+      <c r="G45" s="6"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="J45" s="6"/>
+      <c r="K45" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="L45" s="6"/>
+      <c r="M45" s="6"/>
+      <c r="N45" s="6"/>
+      <c r="O45" s="6"/>
+      <c r="P45" s="6"/>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A46"/>
+      <c r="B46" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C46" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="D46" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="F46" s="5"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="5"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="5"/>
+      <c r="K46" s="5"/>
+      <c r="L46" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M46" s="5"/>
+      <c r="N46" s="5"/>
+      <c r="O46" s="5"/>
+      <c r="P46" s="5"/>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A47" s="3"/>
+      <c r="B47" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D47" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E45" s="5"/>
-      <c r="F45" s="5"/>
-      <c r="G45" s="5"/>
-      <c r="H45" s="5"/>
-      <c r="I45" s="5"/>
-      <c r="J45" s="5"/>
-      <c r="K45" s="5"/>
-      <c r="L45" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M45" s="5"/>
-      <c r="N45" s="5"/>
-      <c r="O45" s="5"/>
-      <c r="P45" s="5"/>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A46" s="3"/>
-      <c r="B46" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E46" s="4"/>
-      <c r="F46" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="G46" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="H46" s="5"/>
-      <c r="I46" s="4"/>
-      <c r="J46" s="4"/>
-      <c r="K46" s="4"/>
-      <c r="L46" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="M46" s="4"/>
-      <c r="N46" s="4"/>
-      <c r="O46" s="4"/>
-      <c r="P46" s="4"/>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B47" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E47" s="4"/>
+      <c r="E47" s="8" t="s">
+        <v>240</v>
+      </c>
       <c r="F47" s="5" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H47" s="5" t="s">
-        <v>172</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="H47" s="5"/>
       <c r="I47" s="4"/>
       <c r="J47" s="4"/>
       <c r="K47" s="4"/>
       <c r="L47" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M47" s="4"/>
       <c r="N47" s="4"/>
@@ -2846,29 +3240,37 @@
       <c r="P47" s="4"/>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B48" s="6" t="s">
+      <c r="B48" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E48" s="5"/>
-      <c r="F48" s="5"/>
-      <c r="G48" s="5"/>
-      <c r="H48" s="5"/>
-      <c r="I48" s="5"/>
-      <c r="J48" s="5"/>
-      <c r="K48" s="5"/>
-      <c r="L48" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M48" s="5"/>
-      <c r="N48" s="5"/>
-      <c r="O48" s="5"/>
-      <c r="P48" s="5"/>
+        <v>52</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H48" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="K48" s="4"/>
+      <c r="L48" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="M48" s="4"/>
+      <c r="N48" s="4"/>
+      <c r="O48" s="4"/>
+      <c r="P48" s="4"/>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B49" s="6" t="s">
@@ -2878,9 +3280,11 @@
         <v>25</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E49" s="5"/>
+        <v>53</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>242</v>
+      </c>
       <c r="F49" s="5"/>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
@@ -2896,115 +3300,117 @@
       <c r="P49" s="5"/>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A50" s="3"/>
-      <c r="B50" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>47</v>
+      <c r="B50" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="D50" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="F50" s="5"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="5"/>
+      <c r="I50" s="5"/>
+      <c r="J50" s="5"/>
+      <c r="K50" s="5"/>
+      <c r="L50" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M50" s="5"/>
+      <c r="N50" s="5"/>
+      <c r="O50" s="5"/>
+      <c r="P50" s="5"/>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A51" s="3"/>
+      <c r="B51" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="H51" s="5"/>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
+      <c r="K51" s="4"/>
+      <c r="L51" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="M51" s="4"/>
+      <c r="N51" s="4"/>
+      <c r="O51" s="4"/>
+      <c r="P51" s="4"/>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B52" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D52" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E50" s="4"/>
-      <c r="F50" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="G50" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="H50" s="5"/>
-      <c r="I50" s="4"/>
-      <c r="J50" s="4"/>
-      <c r="K50" s="4"/>
-      <c r="L50" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="M50" s="4"/>
-      <c r="N50" s="4"/>
-      <c r="O50" s="4"/>
-      <c r="P50" s="4"/>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B51" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D51" s="4" t="s">
+      <c r="E52" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="F52" s="5"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="5"/>
+      <c r="I52" s="5"/>
+      <c r="J52" s="5"/>
+      <c r="K52" s="5"/>
+      <c r="L52" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M52" s="5"/>
+      <c r="N52" s="5"/>
+      <c r="O52" s="5"/>
+      <c r="P52" s="5"/>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A53" s="3"/>
+      <c r="B53" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D53" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="5"/>
-      <c r="H51" s="5"/>
-      <c r="I51" s="5"/>
-      <c r="J51" s="5"/>
-      <c r="K51" s="5"/>
-      <c r="L51" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M51" s="5"/>
-      <c r="N51" s="5"/>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A52" s="3"/>
-      <c r="B52" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E52" s="4"/>
-      <c r="F52" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="G52" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="H52" s="5"/>
-      <c r="I52" s="4"/>
-      <c r="J52" s="4"/>
-      <c r="K52" s="4"/>
-      <c r="L52" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="M52" s="4"/>
-      <c r="N52" s="4"/>
-      <c r="O52" s="4"/>
-      <c r="P52" s="4"/>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B53" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E53" s="4"/>
+      <c r="E53" s="8" t="s">
+        <v>246</v>
+      </c>
       <c r="F53" s="5" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H53" s="5" t="s">
-        <v>160</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="H53" s="5"/>
       <c r="I53" s="4"/>
       <c r="J53" s="4"/>
       <c r="K53" s="4"/>
       <c r="L53" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M53" s="4"/>
       <c r="N53" s="4"/>
@@ -3012,148 +3418,170 @@
       <c r="P53" s="4"/>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C54" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H54" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="I54" s="4"/>
+      <c r="J54" s="4"/>
+      <c r="K54" s="4"/>
+      <c r="L54" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="M54" s="4"/>
+      <c r="N54" s="4"/>
+      <c r="O54" s="4"/>
+      <c r="P54" s="4"/>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B55" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C55" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D54" s="4" t="s">
+      <c r="D55" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="F55" s="5"/>
+      <c r="G55" s="5"/>
+      <c r="H55" s="5"/>
+      <c r="I55" s="5"/>
+      <c r="J55" s="5"/>
+      <c r="K55" s="5"/>
+      <c r="L55" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M55" s="5"/>
+      <c r="N55" s="5"/>
+      <c r="O55" s="5"/>
+      <c r="P55" s="5"/>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B56" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D56" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E54" s="5"/>
-      <c r="F54" s="5"/>
-      <c r="G54" s="5"/>
-      <c r="H54" s="5"/>
-      <c r="I54" s="5"/>
-      <c r="J54" s="5"/>
-      <c r="K54" s="5"/>
-      <c r="L54" s="5" t="s">
+      <c r="E56" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="F56" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H56" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="I56" s="4"/>
+      <c r="J56" s="4"/>
+      <c r="K56" s="4"/>
+      <c r="L56" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="M56" s="4"/>
+      <c r="N56" s="4"/>
+      <c r="O56" s="4"/>
+      <c r="P56" s="4"/>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B57" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="F57" s="5"/>
+      <c r="G57" s="5"/>
+      <c r="H57" s="5"/>
+      <c r="I57" s="5"/>
+      <c r="J57" s="5"/>
+      <c r="K57" s="5"/>
+      <c r="L57" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="M54" s="5"/>
-      <c r="N54" s="5"/>
-      <c r="O54" s="5"/>
-      <c r="P54" s="5"/>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B55" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E55" s="4"/>
-      <c r="F55" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="G55" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H55" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="I55" s="4"/>
-      <c r="J55" s="4"/>
-      <c r="K55" s="4"/>
-      <c r="L55" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="M55" s="4"/>
-      <c r="N55" s="4"/>
-      <c r="O55" s="4"/>
-      <c r="P55" s="4"/>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B56" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E56" s="5"/>
-      <c r="F56" s="5"/>
-      <c r="G56" s="5"/>
-      <c r="H56" s="5"/>
-      <c r="I56" s="5"/>
-      <c r="J56" s="5"/>
-      <c r="K56" s="5"/>
-      <c r="L56" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M56" s="5"/>
-      <c r="N56" s="5"/>
-      <c r="O56" s="5"/>
-      <c r="P56" s="5"/>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B57" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C57" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E57" s="4"/>
-      <c r="F57" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="G57" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H57" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="I57" s="4"/>
-      <c r="J57" s="4"/>
-      <c r="K57" s="4"/>
-      <c r="L57" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="M57" s="4"/>
-      <c r="N57" s="4"/>
-      <c r="O57" s="4"/>
-      <c r="P57" s="4"/>
+      <c r="M57" s="5"/>
+      <c r="N57" s="5"/>
+      <c r="O57" s="5"/>
+      <c r="P57" s="5"/>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B58" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="C58" s="5"/>
-      <c r="D58" s="7"/>
-      <c r="E58" s="8"/>
+        <v>21</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>251</v>
+      </c>
       <c r="F58" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="G58" s="5"/>
-      <c r="H58" s="5"/>
-      <c r="I58" s="7"/>
-      <c r="J58" s="7"/>
-      <c r="K58" s="7"/>
-      <c r="L58" s="7"/>
-      <c r="M58" s="7"/>
-      <c r="N58" s="7"/>
-      <c r="O58" s="7"/>
-      <c r="P58" s="7"/>
+        <v>135</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H58" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="I58" s="4"/>
+      <c r="J58" s="4"/>
+      <c r="K58" s="4"/>
+      <c r="L58" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="M58" s="4"/>
+      <c r="N58" s="4"/>
+      <c r="O58" s="4"/>
+      <c r="P58" s="4"/>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B59" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="C59" s="4"/>
+      <c r="B59" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C59" s="5"/>
       <c r="D59" s="4"/>
-      <c r="E59" s="4"/>
-      <c r="F59" s="4"/>
-      <c r="G59" s="4"/>
-      <c r="H59" s="4"/>
+      <c r="E59" s="8"/>
+      <c r="F59" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="G59" s="5"/>
+      <c r="H59" s="5"/>
       <c r="I59" s="4"/>
       <c r="J59" s="4"/>
       <c r="K59" s="4"/>
@@ -3161,191 +3589,188 @@
       <c r="M59" s="4"/>
       <c r="N59" s="4"/>
       <c r="O59" s="4"/>
-      <c r="P59" s="4" t="s">
-        <v>156</v>
-      </c>
+      <c r="P59" s="4"/>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B60" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C60" s="6"/>
-      <c r="D60" s="6"/>
-      <c r="E60" s="6"/>
-      <c r="F60" s="6"/>
-      <c r="G60" s="6"/>
-      <c r="H60" s="6"/>
-      <c r="I60" s="6"/>
-      <c r="J60" s="6"/>
-      <c r="K60" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L60" s="6"/>
-      <c r="M60" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="N60" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="O60" s="6"/>
-      <c r="P60" s="6"/>
+      <c r="B60" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C60" s="4"/>
+      <c r="D60" s="4"/>
+      <c r="E60" s="8"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
+      <c r="I60" s="4"/>
+      <c r="J60" s="4"/>
+      <c r="K60" s="4"/>
+      <c r="L60" s="4"/>
+      <c r="M60" s="4"/>
+      <c r="N60" s="4"/>
+      <c r="O60" s="4"/>
+      <c r="P60" s="4" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B61" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C61" s="6"/>
       <c r="D61" s="6"/>
-      <c r="E61" s="6"/>
+      <c r="E61" s="8"/>
       <c r="F61" s="6"/>
       <c r="G61" s="6"/>
       <c r="H61" s="6"/>
       <c r="I61" s="6"/>
       <c r="J61" s="6"/>
       <c r="K61" s="6" t="s">
-        <v>166</v>
+        <v>23</v>
       </c>
       <c r="L61" s="6"/>
-      <c r="M61" s="6"/>
-      <c r="N61" s="6"/>
+      <c r="M61" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="N61" s="6" t="s">
+        <v>23</v>
+      </c>
       <c r="O61" s="6"/>
       <c r="P61" s="6"/>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B62" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C62" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="C62" s="6"/>
+      <c r="D62" s="6"/>
+      <c r="E62" s="8"/>
+      <c r="F62" s="6"/>
+      <c r="G62" s="6"/>
+      <c r="H62" s="6"/>
+      <c r="I62" s="6"/>
+      <c r="J62" s="6"/>
+      <c r="K62" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="L62" s="6"/>
+      <c r="M62" s="6"/>
+      <c r="N62" s="6"/>
+      <c r="O62" s="6"/>
+      <c r="P62" s="6"/>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B63" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C63" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D62" s="4" t="s">
+      <c r="D63" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="F63" s="5"/>
+      <c r="G63" s="5"/>
+      <c r="H63" s="5"/>
+      <c r="I63" s="5"/>
+      <c r="J63" s="5"/>
+      <c r="K63" s="5"/>
+      <c r="L63" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M63" s="5"/>
+      <c r="N63" s="5"/>
+      <c r="O63" s="5"/>
+      <c r="P63" s="5"/>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A64" s="3"/>
+      <c r="B64" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D64" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="E62" s="5"/>
-      <c r="F62" s="5"/>
-      <c r="G62" s="5"/>
-      <c r="H62" s="5"/>
-      <c r="I62" s="5"/>
-      <c r="J62" s="5"/>
-      <c r="K62" s="5"/>
-      <c r="L62" s="5" t="s">
+      <c r="E64" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="F64" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="G64" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="H64" s="5"/>
+      <c r="I64" s="4"/>
+      <c r="J64" s="4"/>
+      <c r="K64" s="4"/>
+      <c r="L64" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="M64" s="4"/>
+      <c r="N64" s="4"/>
+      <c r="O64" s="4"/>
+      <c r="P64" s="4"/>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B65" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="F65" s="5"/>
+      <c r="G65" s="5"/>
+      <c r="H65" s="5"/>
+      <c r="I65" s="5"/>
+      <c r="J65" s="5"/>
+      <c r="K65" s="5"/>
+      <c r="L65" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="M62" s="5"/>
-      <c r="N62" s="5"/>
-      <c r="O62" s="5"/>
-      <c r="P62" s="5"/>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A63" s="3"/>
-      <c r="B63" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C63" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E63" s="4"/>
-      <c r="F63" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="G63" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="H63" s="5"/>
-      <c r="I63" s="4"/>
-      <c r="J63" s="4"/>
-      <c r="K63" s="4"/>
-      <c r="L63" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="M63" s="4"/>
-      <c r="N63" s="4"/>
-      <c r="O63" s="4"/>
-      <c r="P63" s="4"/>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B64" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C64" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D64" s="4" t="s">
+      <c r="M65" s="5"/>
+      <c r="N65" s="5"/>
+      <c r="O65" s="5"/>
+      <c r="P65" s="5"/>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B66" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D66" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="E64" s="5"/>
-      <c r="F64" s="5"/>
-      <c r="G64" s="5"/>
-      <c r="H64" s="5"/>
-      <c r="I64" s="5"/>
-      <c r="J64" s="5"/>
-      <c r="K64" s="5"/>
-      <c r="L64" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M64" s="5"/>
-      <c r="N64" s="5"/>
-      <c r="O64" s="5"/>
-      <c r="P64" s="5"/>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B65" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E65" s="4"/>
-      <c r="F65" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="G65" s="5" t="s">
+      <c r="E66" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="F66" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="G66" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="H65" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="I65" s="4"/>
-      <c r="J65" s="4"/>
-      <c r="K65" s="4"/>
-      <c r="L65" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="M65" s="4"/>
-      <c r="N65" s="4"/>
-      <c r="O65" s="4"/>
-      <c r="P65" s="4"/>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A66" s="3"/>
-      <c r="B66" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C66" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D66" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E66" s="4"/>
-      <c r="F66" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="G66" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="H66" s="5"/>
+      <c r="H66" s="5" t="s">
+        <v>156</v>
+      </c>
       <c r="I66" s="4"/>
       <c r="J66" s="4"/>
       <c r="K66" s="4"/>
       <c r="L66" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M66" s="4"/>
       <c r="N66" s="4"/>
@@ -3353,30 +3778,31 @@
       <c r="P66" s="4"/>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A67" s="3"/>
       <c r="B67" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C67" s="5" t="s">
-        <v>24</v>
+      <c r="C67" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E67" s="4"/>
+        <v>67</v>
+      </c>
+      <c r="E67" s="8" t="s">
+        <v>256</v>
+      </c>
       <c r="F67" s="5" t="s">
-        <v>136</v>
+        <v>170</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H67" s="5" t="s">
-        <v>177</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="H67" s="5"/>
       <c r="I67" s="4"/>
       <c r="J67" s="4"/>
       <c r="K67" s="4"/>
       <c r="L67" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M67" s="4"/>
       <c r="N67" s="4"/>
@@ -3384,29 +3810,32 @@
       <c r="P67" s="4"/>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A68" s="3"/>
       <c r="B68" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C68" s="4" t="s">
-        <v>47</v>
+      <c r="C68" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E68" s="4"/>
+        <v>68</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>257</v>
+      </c>
       <c r="F68" s="5" t="s">
-        <v>174</v>
+        <v>135</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="H68" s="5"/>
+        <v>22</v>
+      </c>
+      <c r="H68" s="5" t="s">
+        <v>173</v>
+      </c>
       <c r="I68" s="4"/>
       <c r="J68" s="4"/>
       <c r="K68" s="4"/>
       <c r="L68" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M68" s="4"/>
       <c r="N68" s="4"/>
@@ -3414,30 +3843,31 @@
       <c r="P68" s="4"/>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A69" s="3"/>
       <c r="B69" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C69" s="5" t="s">
-        <v>24</v>
+      <c r="C69" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="E69" s="4"/>
+        <v>69</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>258</v>
+      </c>
       <c r="F69" s="5" t="s">
-        <v>136</v>
+        <v>170</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H69" s="5" t="s">
-        <v>178</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="H69" s="5"/>
       <c r="I69" s="4"/>
       <c r="J69" s="4"/>
       <c r="K69" s="4"/>
       <c r="L69" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M69" s="4"/>
       <c r="N69" s="4"/>
@@ -3445,60 +3875,64 @@
       <c r="P69" s="4"/>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C70" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E70" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="F70" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="G70" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H70" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="I70" s="4"/>
+      <c r="J70" s="4"/>
+      <c r="K70" s="4"/>
+      <c r="L70" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="M70" s="4"/>
+      <c r="N70" s="4"/>
+      <c r="O70" s="4"/>
+      <c r="P70" s="4"/>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B71" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C71" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D70" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="E70" s="5"/>
-      <c r="F70" s="5"/>
-      <c r="G70" s="5"/>
-      <c r="H70" s="5"/>
-      <c r="I70" s="5"/>
-      <c r="J70" s="5"/>
-      <c r="K70" s="5"/>
-      <c r="L70" s="5" t="s">
+      <c r="D71" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="E71" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="F71" s="5"/>
+      <c r="G71" s="5"/>
+      <c r="H71" s="5"/>
+      <c r="I71" s="5"/>
+      <c r="J71" s="5"/>
+      <c r="K71" s="5"/>
+      <c r="L71" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="M70" s="5"/>
-      <c r="N70" s="5"/>
-      <c r="O70" s="5"/>
-      <c r="P70" s="5"/>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B71" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C71" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D71" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E71" s="4"/>
-      <c r="F71" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="G71" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H71" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="I71" s="4"/>
-      <c r="J71" s="4"/>
-      <c r="K71" s="4"/>
-      <c r="L71" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="M71" s="4"/>
-      <c r="N71" s="4"/>
-      <c r="O71" s="4"/>
-      <c r="P71" s="4"/>
+      <c r="M71" s="5"/>
+      <c r="N71" s="5"/>
+      <c r="O71" s="5"/>
+      <c r="P71" s="5"/>
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B72" s="5" t="s">
@@ -3508,23 +3942,25 @@
         <v>24</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="E72" s="4"/>
+        <v>71</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>261</v>
+      </c>
       <c r="F72" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G72" s="5" t="s">
         <v>22</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="I72" s="4"/>
       <c r="J72" s="4"/>
       <c r="K72" s="4"/>
       <c r="L72" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M72" s="4"/>
       <c r="N72" s="4"/>
@@ -3532,29 +3968,32 @@
       <c r="P72" s="4"/>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A73" s="3"/>
       <c r="B73" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C73" s="4" t="s">
-        <v>47</v>
+      <c r="C73" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E73" s="4"/>
+        <v>72</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>262</v>
+      </c>
       <c r="F73" s="5" t="s">
-        <v>174</v>
+        <v>135</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="H73" s="5"/>
+        <v>22</v>
+      </c>
+      <c r="H73" s="5" t="s">
+        <v>157</v>
+      </c>
       <c r="I73" s="4"/>
       <c r="J73" s="4"/>
       <c r="K73" s="4"/>
       <c r="L73" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M73" s="4"/>
       <c r="N73" s="4"/>
@@ -3562,30 +4001,31 @@
       <c r="P73" s="4"/>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A74" s="3"/>
       <c r="B74" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C74" s="5" t="s">
-        <v>24</v>
+      <c r="C74" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E74" s="4"/>
+        <v>73</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>263</v>
+      </c>
       <c r="F74" s="5" t="s">
-        <v>136</v>
+        <v>170</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H74" s="5" t="s">
-        <v>183</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="H74" s="5"/>
       <c r="I74" s="4"/>
       <c r="J74" s="4"/>
       <c r="K74" s="4"/>
       <c r="L74" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M74" s="4"/>
       <c r="N74" s="4"/>
@@ -3593,29 +4033,32 @@
       <c r="P74" s="4"/>
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A75" s="3"/>
       <c r="B75" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C75" s="4" t="s">
-        <v>47</v>
+      <c r="C75" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="E75" s="4"/>
+        <v>74</v>
+      </c>
+      <c r="E75" s="8" t="s">
+        <v>264</v>
+      </c>
       <c r="F75" s="5" t="s">
-        <v>174</v>
+        <v>135</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="H75" s="5"/>
+        <v>22</v>
+      </c>
+      <c r="H75" s="5" t="s">
+        <v>179</v>
+      </c>
       <c r="I75" s="4"/>
       <c r="J75" s="4"/>
       <c r="K75" s="4"/>
       <c r="L75" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M75" s="4"/>
       <c r="N75" s="4"/>
@@ -3623,36 +4066,49 @@
       <c r="P75" s="4"/>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A76" s="3"/>
       <c r="B76" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="C76" s="5"/>
-      <c r="D76" s="7"/>
-      <c r="E76" s="8"/>
+        <v>21</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E76" s="8" t="s">
+        <v>265</v>
+      </c>
       <c r="F76" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="G76" s="5"/>
+        <v>170</v>
+      </c>
+      <c r="G76" s="5" t="s">
+        <v>150</v>
+      </c>
       <c r="H76" s="5"/>
-      <c r="I76" s="7"/>
-      <c r="J76" s="7"/>
-      <c r="K76" s="7"/>
-      <c r="L76" s="7"/>
-      <c r="M76" s="7"/>
-      <c r="N76" s="7"/>
-      <c r="O76" s="7"/>
-      <c r="P76" s="7"/>
+      <c r="I76" s="4"/>
+      <c r="J76" s="4"/>
+      <c r="K76" s="4"/>
+      <c r="L76" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="M76" s="4"/>
+      <c r="N76" s="4"/>
+      <c r="O76" s="4"/>
+      <c r="P76" s="4"/>
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B77" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="C77" s="4"/>
+      <c r="B77" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C77" s="5"/>
       <c r="D77" s="4"/>
-      <c r="E77" s="4"/>
-      <c r="F77" s="4"/>
-      <c r="G77" s="4"/>
-      <c r="H77" s="4"/>
+      <c r="E77" s="8"/>
+      <c r="F77" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="G77" s="5"/>
+      <c r="H77" s="5"/>
       <c r="I77" s="4"/>
       <c r="J77" s="4"/>
       <c r="K77" s="4"/>
@@ -3660,112 +4116,102 @@
       <c r="M77" s="4"/>
       <c r="N77" s="4"/>
       <c r="O77" s="4"/>
-      <c r="P77" s="4" t="s">
-        <v>156</v>
-      </c>
+      <c r="P77" s="4"/>
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B78" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C78" s="6"/>
-      <c r="D78" s="6"/>
-      <c r="E78" s="6"/>
-      <c r="F78" s="6"/>
-      <c r="G78" s="6"/>
-      <c r="H78" s="6"/>
-      <c r="I78" s="6"/>
-      <c r="J78" s="6"/>
-      <c r="K78" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L78" s="6"/>
-      <c r="M78" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="N78" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="O78" s="6"/>
-      <c r="P78" s="6"/>
+      <c r="B78" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C78" s="4"/>
+      <c r="D78" s="4"/>
+      <c r="E78" s="8"/>
+      <c r="F78" s="4"/>
+      <c r="G78" s="4"/>
+      <c r="H78" s="4"/>
+      <c r="I78" s="4"/>
+      <c r="J78" s="4"/>
+      <c r="K78" s="4"/>
+      <c r="L78" s="4"/>
+      <c r="M78" s="4"/>
+      <c r="N78" s="4"/>
+      <c r="O78" s="4"/>
+      <c r="P78" s="4" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B79" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C79" s="6"/>
       <c r="D79" s="6"/>
-      <c r="E79" s="6"/>
+      <c r="E79" s="8"/>
       <c r="F79" s="6"/>
       <c r="G79" s="6"/>
       <c r="H79" s="6"/>
       <c r="I79" s="6"/>
       <c r="J79" s="6"/>
       <c r="K79" s="6" t="s">
-        <v>166</v>
+        <v>23</v>
       </c>
       <c r="L79" s="6"/>
-      <c r="M79" s="6"/>
-      <c r="N79" s="6"/>
+      <c r="M79" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="N79" s="6" t="s">
+        <v>23</v>
+      </c>
       <c r="O79" s="6"/>
       <c r="P79" s="6"/>
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B80" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C80" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D80" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E80" s="4"/>
-      <c r="F80" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="G80" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="H80" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="I80" s="4"/>
-      <c r="J80" s="4"/>
-      <c r="K80" s="4"/>
-      <c r="L80" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="M80" s="4"/>
-      <c r="N80" s="4"/>
-      <c r="O80" s="4"/>
-      <c r="P80" s="4"/>
+      <c r="B80" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C80" s="6"/>
+      <c r="D80" s="6"/>
+      <c r="E80" s="8"/>
+      <c r="F80" s="6"/>
+      <c r="G80" s="6"/>
+      <c r="H80" s="6"/>
+      <c r="I80" s="6"/>
+      <c r="J80" s="6"/>
+      <c r="K80" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="L80" s="6"/>
+      <c r="M80" s="6"/>
+      <c r="N80" s="6"/>
+      <c r="O80" s="6"/>
+      <c r="P80" s="6"/>
     </row>
     <row r="81" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B81" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C81" s="5" t="s">
-        <v>24</v>
+      <c r="C81" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E81" s="4"/>
+        <v>76</v>
+      </c>
+      <c r="E81" s="8" t="s">
+        <v>266</v>
+      </c>
       <c r="F81" s="5" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>22</v>
+        <v>150</v>
       </c>
       <c r="H81" s="5" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="I81" s="4"/>
       <c r="J81" s="4"/>
       <c r="K81" s="4"/>
       <c r="L81" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M81" s="4"/>
       <c r="N81" s="4"/>
@@ -3776,27 +4222,29 @@
       <c r="B82" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C82" s="4" t="s">
-        <v>47</v>
+      <c r="C82" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E82" s="4"/>
+        <v>77</v>
+      </c>
+      <c r="E82" s="8" t="s">
+        <v>267</v>
+      </c>
       <c r="F82" s="5" t="s">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>151</v>
+        <v>22</v>
       </c>
       <c r="H82" s="5" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="I82" s="4"/>
       <c r="J82" s="4"/>
       <c r="K82" s="4"/>
       <c r="L82" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M82" s="4"/>
       <c r="N82" s="4"/>
@@ -3807,27 +4255,29 @@
       <c r="B83" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C83" s="5" t="s">
-        <v>24</v>
+      <c r="C83" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E83" s="4"/>
+        <v>78</v>
+      </c>
+      <c r="E83" s="8" t="s">
+        <v>268</v>
+      </c>
       <c r="F83" s="5" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>22</v>
+        <v>150</v>
       </c>
       <c r="H83" s="5" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I83" s="4"/>
       <c r="J83" s="4"/>
       <c r="K83" s="4"/>
       <c r="L83" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M83" s="4"/>
       <c r="N83" s="4"/>
@@ -3838,27 +4288,29 @@
       <c r="B84" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C84" s="4" t="s">
-        <v>47</v>
+      <c r="C84" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E84" s="4"/>
+        <v>79</v>
+      </c>
+      <c r="E84" s="8" t="s">
+        <v>269</v>
+      </c>
       <c r="F84" s="5" t="s">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>151</v>
+        <v>22</v>
       </c>
       <c r="H84" s="5" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="I84" s="4"/>
       <c r="J84" s="4"/>
       <c r="K84" s="4"/>
       <c r="L84" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M84" s="4"/>
       <c r="N84" s="4"/>
@@ -3869,27 +4321,29 @@
       <c r="B85" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C85" s="5" t="s">
-        <v>24</v>
+      <c r="C85" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="E85" s="4"/>
+        <v>80</v>
+      </c>
+      <c r="E85" s="8" t="s">
+        <v>270</v>
+      </c>
       <c r="F85" s="5" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>22</v>
+        <v>150</v>
       </c>
       <c r="H85" s="5" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="I85" s="4"/>
       <c r="J85" s="4"/>
       <c r="K85" s="4"/>
       <c r="L85" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M85" s="4"/>
       <c r="N85" s="4"/>
@@ -3900,27 +4354,29 @@
       <c r="B86" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C86" s="4" t="s">
-        <v>47</v>
+      <c r="C86" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="E86" s="4"/>
+        <v>81</v>
+      </c>
+      <c r="E86" s="8" t="s">
+        <v>271</v>
+      </c>
       <c r="F86" s="5" t="s">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>151</v>
+        <v>22</v>
       </c>
       <c r="H86" s="5" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I86" s="4"/>
       <c r="J86" s="4"/>
       <c r="K86" s="4"/>
       <c r="L86" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M86" s="4"/>
       <c r="N86" s="4"/>
@@ -3928,86 +4384,92 @@
       <c r="P86" s="4"/>
     </row>
     <row r="87" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B87" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C87" s="5" t="s">
+      <c r="B87" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E87" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="F87" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="G87" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="H87" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="I87" s="4"/>
+      <c r="J87" s="4"/>
+      <c r="K87" s="4"/>
+      <c r="L87" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="M87" s="4"/>
+      <c r="N87" s="4"/>
+      <c r="O87" s="4"/>
+      <c r="P87" s="4"/>
+    </row>
+    <row r="88" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B88" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C88" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D87" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="E87" s="5"/>
-      <c r="F87" s="5"/>
-      <c r="G87" s="5"/>
-      <c r="H87" s="5"/>
-      <c r="I87" s="5"/>
-      <c r="J87" s="5"/>
-      <c r="K87" s="5"/>
-      <c r="L87" s="5" t="s">
+      <c r="D88" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E88" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="F88" s="5"/>
+      <c r="G88" s="5"/>
+      <c r="H88" s="5"/>
+      <c r="I88" s="5"/>
+      <c r="J88" s="5"/>
+      <c r="K88" s="5"/>
+      <c r="L88" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="M87" s="5"/>
-      <c r="N87" s="5"/>
-      <c r="O87" s="5"/>
-      <c r="P87" s="5"/>
-    </row>
-    <row r="88" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B88" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C88" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D88" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="E88" s="4"/>
-      <c r="F88" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="G88" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="H88" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="I88" s="4"/>
-      <c r="J88" s="4"/>
-      <c r="K88" s="4"/>
-      <c r="L88" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="M88" s="4"/>
-      <c r="N88" s="4"/>
-      <c r="O88" s="4"/>
-      <c r="P88" s="4"/>
+      <c r="M88" s="5"/>
+      <c r="N88" s="5"/>
+      <c r="O88" s="5"/>
+      <c r="P88" s="5"/>
     </row>
     <row r="89" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B89" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C89" s="5" t="s">
-        <v>24</v>
+      <c r="C89" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="E89" s="4"/>
+        <v>84</v>
+      </c>
+      <c r="E89" s="8" t="s">
+        <v>274</v>
+      </c>
       <c r="F89" s="5" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>22</v>
+        <v>150</v>
       </c>
       <c r="H89" s="5" t="s">
-        <v>159</v>
+        <v>187</v>
       </c>
       <c r="I89" s="4"/>
       <c r="J89" s="4"/>
       <c r="K89" s="4"/>
       <c r="L89" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M89" s="4"/>
       <c r="N89" s="4"/>
@@ -4018,27 +4480,29 @@
       <c r="B90" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C90" s="4" t="s">
-        <v>47</v>
+      <c r="C90" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E90" s="4"/>
+        <v>85</v>
+      </c>
+      <c r="E90" s="8" t="s">
+        <v>275</v>
+      </c>
       <c r="F90" s="5" t="s">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>151</v>
+        <v>22</v>
       </c>
       <c r="H90" s="5" t="s">
-        <v>192</v>
+        <v>156</v>
       </c>
       <c r="I90" s="4"/>
       <c r="J90" s="4"/>
       <c r="K90" s="4"/>
       <c r="L90" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M90" s="4"/>
       <c r="N90" s="4"/>
@@ -4049,27 +4513,29 @@
       <c r="B91" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C91" s="5" t="s">
-        <v>24</v>
+      <c r="C91" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="E91" s="4"/>
+        <v>86</v>
+      </c>
+      <c r="E91" s="8" t="s">
+        <v>276</v>
+      </c>
       <c r="F91" s="5" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>22</v>
+        <v>150</v>
       </c>
       <c r="H91" s="5" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="I91" s="4"/>
       <c r="J91" s="4"/>
       <c r="K91" s="4"/>
       <c r="L91" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M91" s="4"/>
       <c r="N91" s="4"/>
@@ -4077,128 +4543,132 @@
       <c r="P91" s="4"/>
     </row>
     <row r="92" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B92" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="C92" s="4"/>
-      <c r="D92" s="4"/>
-      <c r="E92" s="4"/>
-      <c r="F92" s="4"/>
-      <c r="G92" s="4"/>
-      <c r="H92" s="4"/>
+      <c r="B92" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E92" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="F92" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="G92" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H92" s="5" t="s">
+        <v>169</v>
+      </c>
       <c r="I92" s="4"/>
       <c r="J92" s="4"/>
       <c r="K92" s="4"/>
-      <c r="L92" s="4"/>
+      <c r="L92" s="4" t="s">
+        <v>138</v>
+      </c>
       <c r="M92" s="4"/>
       <c r="N92" s="4"/>
       <c r="O92" s="4"/>
-      <c r="P92" s="4" t="s">
-        <v>156</v>
-      </c>
+      <c r="P92" s="4"/>
     </row>
     <row r="93" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B93" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C93" s="6"/>
-      <c r="D93" s="6"/>
-      <c r="E93" s="6"/>
-      <c r="F93" s="6"/>
-      <c r="G93" s="6"/>
-      <c r="H93" s="6"/>
-      <c r="I93" s="6"/>
-      <c r="J93" s="6"/>
-      <c r="K93" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L93" s="6"/>
-      <c r="M93" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="N93" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="O93" s="6"/>
-      <c r="P93" s="6"/>
+      <c r="B93" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C93" s="4"/>
+      <c r="D93" s="4"/>
+      <c r="E93" s="8"/>
+      <c r="F93" s="4"/>
+      <c r="G93" s="4"/>
+      <c r="H93" s="4"/>
+      <c r="I93" s="4"/>
+      <c r="J93" s="4"/>
+      <c r="K93" s="4"/>
+      <c r="L93" s="4"/>
+      <c r="M93" s="4"/>
+      <c r="N93" s="4"/>
+      <c r="O93" s="4"/>
+      <c r="P93" s="4" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="94" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B94" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="6"/>
-      <c r="E94" s="6"/>
+      <c r="E94" s="8"/>
       <c r="F94" s="6"/>
       <c r="G94" s="6"/>
       <c r="H94" s="6"/>
       <c r="I94" s="6"/>
       <c r="J94" s="6"/>
       <c r="K94" s="6" t="s">
-        <v>193</v>
+        <v>23</v>
       </c>
       <c r="L94" s="6"/>
-      <c r="M94" s="6"/>
-      <c r="N94" s="6"/>
+      <c r="M94" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="N94" s="6" t="s">
+        <v>23</v>
+      </c>
       <c r="O94" s="6"/>
       <c r="P94" s="6"/>
     </row>
     <row r="95" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B95" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C95" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D95" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="E95" s="4"/>
-      <c r="F95" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="G95" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="H95" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="I95" s="4"/>
-      <c r="J95" s="4"/>
-      <c r="K95" s="4"/>
-      <c r="L95" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="M95" s="4"/>
-      <c r="N95" s="4"/>
-      <c r="O95" s="4"/>
-      <c r="P95" s="4"/>
+      <c r="B95" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C95" s="6"/>
+      <c r="D95" s="6"/>
+      <c r="E95" s="8"/>
+      <c r="F95" s="6"/>
+      <c r="G95" s="6"/>
+      <c r="H95" s="6"/>
+      <c r="I95" s="6"/>
+      <c r="J95" s="6"/>
+      <c r="K95" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="L95" s="6"/>
+      <c r="M95" s="6"/>
+      <c r="N95" s="6"/>
+      <c r="O95" s="6"/>
+      <c r="P95" s="6"/>
     </row>
     <row r="96" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B96" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C96" s="5" t="s">
-        <v>24</v>
+      <c r="C96" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="E96" s="4"/>
+        <v>88</v>
+      </c>
+      <c r="E96" s="8" t="s">
+        <v>278</v>
+      </c>
       <c r="F96" s="5" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="G96" s="5" t="s">
-        <v>22</v>
+        <v>150</v>
       </c>
       <c r="H96" s="5" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="I96" s="4"/>
       <c r="J96" s="4"/>
       <c r="K96" s="4"/>
       <c r="L96" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M96" s="4"/>
       <c r="N96" s="4"/>
@@ -4209,27 +4679,29 @@
       <c r="B97" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C97" s="4" t="s">
-        <v>47</v>
+      <c r="C97" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="E97" s="4"/>
+        <v>89</v>
+      </c>
+      <c r="E97" s="8" t="s">
+        <v>279</v>
+      </c>
       <c r="F97" s="5" t="s">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>151</v>
+        <v>22</v>
       </c>
       <c r="H97" s="5" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="I97" s="4"/>
       <c r="J97" s="4"/>
       <c r="K97" s="4"/>
       <c r="L97" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M97" s="4"/>
       <c r="N97" s="4"/>
@@ -4237,86 +4709,92 @@
       <c r="P97" s="4"/>
     </row>
     <row r="98" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B98" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C98" s="5" t="s">
-        <v>196</v>
+      <c r="B98" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="E98" s="5"/>
-      <c r="F98" s="5"/>
-      <c r="G98" s="5"/>
-      <c r="H98" s="5"/>
-      <c r="I98" s="5"/>
-      <c r="J98" s="5"/>
-      <c r="K98" s="5"/>
-      <c r="L98" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E98" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="F98" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="G98" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="H98" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="I98" s="4"/>
+      <c r="J98" s="4"/>
+      <c r="K98" s="4"/>
+      <c r="L98" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="M98" s="4"/>
+      <c r="N98" s="4"/>
+      <c r="O98" s="4"/>
+      <c r="P98" s="4"/>
+    </row>
+    <row r="99" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B99" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E99" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="F99" s="5"/>
+      <c r="G99" s="5"/>
+      <c r="H99" s="5"/>
+      <c r="I99" s="5"/>
+      <c r="J99" s="5"/>
+      <c r="K99" s="5"/>
+      <c r="L99" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="M98" s="5"/>
-      <c r="N98" s="5"/>
-      <c r="O98" s="5"/>
-      <c r="P98" s="5"/>
-    </row>
-    <row r="99" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B99" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C99" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D99" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="E99" s="4"/>
-      <c r="F99" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="G99" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H99" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="I99" s="4"/>
-      <c r="J99" s="4"/>
-      <c r="K99" s="4"/>
-      <c r="L99" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="M99" s="4"/>
-      <c r="N99" s="4"/>
-      <c r="O99" s="4"/>
-      <c r="P99" s="4"/>
+      <c r="M99" s="5"/>
+      <c r="N99" s="5"/>
+      <c r="O99" s="5"/>
+      <c r="P99" s="5"/>
     </row>
     <row r="100" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B100" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C100" s="4" t="s">
-        <v>47</v>
+      <c r="C100" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="E100" s="4"/>
+        <v>92</v>
+      </c>
+      <c r="E100" s="8" t="s">
+        <v>282</v>
+      </c>
       <c r="F100" s="5" t="s">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>151</v>
+        <v>22</v>
       </c>
       <c r="H100" s="5" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="I100" s="4"/>
       <c r="J100" s="4"/>
       <c r="K100" s="4"/>
       <c r="L100" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M100" s="4"/>
       <c r="N100" s="4"/>
@@ -4328,20 +4806,28 @@
         <v>21</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="E101" s="4"/>
-      <c r="F101" s="5"/>
-      <c r="G101" s="5"/>
-      <c r="H101" s="5"/>
+        <v>93</v>
+      </c>
+      <c r="E101" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="F101" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="G101" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="H101" s="5" t="s">
+        <v>194</v>
+      </c>
       <c r="I101" s="4"/>
       <c r="J101" s="4"/>
       <c r="K101" s="4"/>
       <c r="L101" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M101" s="4"/>
       <c r="N101" s="4"/>
@@ -4352,27 +4838,23 @@
       <c r="B102" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C102" s="5" t="s">
-        <v>24</v>
+      <c r="C102" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="E102" s="4"/>
-      <c r="F102" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="G102" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H102" s="5" t="s">
-        <v>160</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="E102" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="F102" s="5"/>
+      <c r="G102" s="5"/>
+      <c r="H102" s="5"/>
       <c r="I102" s="4"/>
       <c r="J102" s="4"/>
       <c r="K102" s="4"/>
       <c r="L102" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M102" s="4"/>
       <c r="N102" s="4"/>
@@ -4380,142 +4862,152 @@
       <c r="P102" s="4"/>
     </row>
     <row r="103" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B103" s="6" t="s">
+      <c r="B103" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>196</v>
+        <v>24</v>
       </c>
       <c r="D103" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E103" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F103" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="G103" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H103" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="I103" s="4"/>
+      <c r="J103" s="4"/>
+      <c r="K103" s="4"/>
+      <c r="L103" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="M103" s="4"/>
+      <c r="N103" s="4"/>
+      <c r="O103" s="4"/>
+      <c r="P103" s="4"/>
+    </row>
+    <row r="104" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B104" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E104" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="F104" s="5"/>
+      <c r="G104" s="5"/>
+      <c r="H104" s="5"/>
+      <c r="I104" s="5"/>
+      <c r="J104" s="5"/>
+      <c r="K104" s="5"/>
+      <c r="L104" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M104" s="5"/>
+      <c r="N104" s="5"/>
+      <c r="O104" s="5"/>
+      <c r="P104" s="5"/>
+    </row>
+    <row r="105" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B105" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D105" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="E103" s="5"/>
-      <c r="F103" s="5"/>
-      <c r="G103" s="5"/>
-      <c r="H103" s="5"/>
-      <c r="I103" s="5"/>
-      <c r="J103" s="5"/>
-      <c r="K103" s="5"/>
-      <c r="L103" s="5" t="s">
+      <c r="E105" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="F105" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="G105" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="H105" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="I105" s="4"/>
+      <c r="J105" s="4"/>
+      <c r="K105" s="4"/>
+      <c r="L105" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="M105" s="4"/>
+      <c r="N105" s="4"/>
+      <c r="O105" s="4"/>
+      <c r="P105" s="4"/>
+    </row>
+    <row r="106" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B106" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E106" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="F106" s="5"/>
+      <c r="G106" s="5"/>
+      <c r="H106" s="5"/>
+      <c r="I106" s="5"/>
+      <c r="J106" s="5"/>
+      <c r="K106" s="5"/>
+      <c r="L106" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="M103" s="5"/>
-      <c r="N103" s="5"/>
-      <c r="O103" s="5"/>
-      <c r="P103" s="5"/>
-    </row>
-    <row r="104" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B104" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C104" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D104" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="E104" s="4"/>
-      <c r="F104" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="G104" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="H104" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="I104" s="4"/>
-      <c r="J104" s="4"/>
-      <c r="K104" s="4"/>
-      <c r="L104" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="M104" s="4"/>
-      <c r="N104" s="4"/>
-      <c r="O104" s="4"/>
-      <c r="P104" s="4"/>
-    </row>
-    <row r="105" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B105" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C105" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="D105" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="E105" s="5"/>
-      <c r="F105" s="5"/>
-      <c r="G105" s="5"/>
-      <c r="H105" s="5"/>
-      <c r="I105" s="5"/>
-      <c r="J105" s="5"/>
-      <c r="K105" s="5"/>
-      <c r="L105" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M105" s="5"/>
-      <c r="N105" s="5"/>
-      <c r="O105" s="5"/>
-      <c r="P105" s="5"/>
-    </row>
-    <row r="106" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B106" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C106" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D106" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="E106" s="4"/>
-      <c r="F106" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="G106" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="H106" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="I106" s="4"/>
-      <c r="J106" s="4"/>
-      <c r="K106" s="4"/>
-      <c r="L106" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="M106" s="4"/>
-      <c r="N106" s="4"/>
-      <c r="O106" s="4"/>
-      <c r="P106" s="4"/>
+      <c r="M106" s="5"/>
+      <c r="N106" s="5"/>
+      <c r="O106" s="5"/>
+      <c r="P106" s="5"/>
     </row>
     <row r="107" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B107" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="E107" s="4"/>
+        <v>99</v>
+      </c>
+      <c r="E107" s="8" t="s">
+        <v>289</v>
+      </c>
       <c r="F107" s="5" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H107" s="5" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="I107" s="4"/>
       <c r="J107" s="4"/>
       <c r="K107" s="4"/>
       <c r="L107" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M107" s="4"/>
       <c r="N107" s="4"/>
@@ -4526,27 +5018,29 @@
       <c r="B108" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C108" s="5" t="s">
-        <v>24</v>
+      <c r="C108" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E108" s="4"/>
+        <v>100</v>
+      </c>
+      <c r="E108" s="8" t="s">
+        <v>290</v>
+      </c>
       <c r="F108" s="5" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="G108" s="5" t="s">
-        <v>22</v>
+        <v>150</v>
       </c>
       <c r="H108" s="5" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="I108" s="4"/>
       <c r="J108" s="4"/>
       <c r="K108" s="4"/>
       <c r="L108" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M108" s="4"/>
       <c r="N108" s="4"/>
@@ -4557,27 +5051,29 @@
       <c r="B109" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C109" s="4" t="s">
-        <v>47</v>
+      <c r="C109" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="E109" s="4"/>
+        <v>42</v>
+      </c>
+      <c r="E109" s="8" t="s">
+        <v>291</v>
+      </c>
       <c r="F109" s="5" t="s">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="G109" s="5" t="s">
-        <v>151</v>
+        <v>22</v>
       </c>
       <c r="H109" s="5" t="s">
-        <v>201</v>
+        <v>178</v>
       </c>
       <c r="I109" s="4"/>
       <c r="J109" s="4"/>
       <c r="K109" s="4"/>
       <c r="L109" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M109" s="4"/>
       <c r="N109" s="4"/>
@@ -4588,27 +5084,29 @@
       <c r="B110" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C110" s="5" t="s">
-        <v>24</v>
+      <c r="C110" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="E110" s="4"/>
+        <v>198</v>
+      </c>
+      <c r="E110" s="8" t="s">
+        <v>292</v>
+      </c>
       <c r="F110" s="5" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="G110" s="5" t="s">
-        <v>22</v>
+        <v>150</v>
       </c>
       <c r="H110" s="5" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="I110" s="4"/>
       <c r="J110" s="4"/>
       <c r="K110" s="4"/>
       <c r="L110" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M110" s="4"/>
       <c r="N110" s="4"/>
@@ -4619,27 +5117,29 @@
       <c r="B111" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C111" s="4" t="s">
-        <v>47</v>
+      <c r="C111" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="E111" s="4"/>
+        <v>101</v>
+      </c>
+      <c r="E111" s="8" t="s">
+        <v>293</v>
+      </c>
       <c r="F111" s="5" t="s">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="G111" s="5" t="s">
-        <v>151</v>
+        <v>22</v>
       </c>
       <c r="H111" s="5" t="s">
-        <v>203</v>
+        <v>176</v>
       </c>
       <c r="I111" s="4"/>
       <c r="J111" s="4"/>
       <c r="K111" s="4"/>
       <c r="L111" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M111" s="4"/>
       <c r="N111" s="4"/>
@@ -4647,198 +5147,212 @@
       <c r="P111" s="4"/>
     </row>
     <row r="112" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B112" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C112" s="5" t="s">
-        <v>196</v>
+      <c r="B112" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="D112" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E112" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="F112" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="G112" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="H112" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="I112" s="4"/>
+      <c r="J112" s="4"/>
+      <c r="K112" s="4"/>
+      <c r="L112" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="M112" s="4"/>
+      <c r="N112" s="4"/>
+      <c r="O112" s="4"/>
+      <c r="P112" s="4"/>
+    </row>
+    <row r="113" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B113" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C113" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="D113" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E113" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="F113" s="5"/>
+      <c r="G113" s="5"/>
+      <c r="H113" s="5"/>
+      <c r="I113" s="5"/>
+      <c r="J113" s="5"/>
+      <c r="K113" s="5"/>
+      <c r="L113" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M113" s="5"/>
+      <c r="N113" s="5"/>
+      <c r="O113" s="5"/>
+      <c r="P113" s="5"/>
+    </row>
+    <row r="114" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B114" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D114" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E112" s="5"/>
-      <c r="F112" s="5"/>
-      <c r="G112" s="5"/>
-      <c r="H112" s="5"/>
-      <c r="I112" s="5"/>
-      <c r="J112" s="5"/>
-      <c r="K112" s="5"/>
-      <c r="L112" s="5" t="s">
+      <c r="E114" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="F114" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="G114" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="H114" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="I114" s="4"/>
+      <c r="J114" s="4"/>
+      <c r="K114" s="4"/>
+      <c r="L114" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="M114" s="4"/>
+      <c r="N114" s="4"/>
+      <c r="O114" s="4"/>
+      <c r="P114" s="4"/>
+    </row>
+    <row r="115" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B115" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C115" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="D115" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="E115" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="F115" s="5"/>
+      <c r="G115" s="5"/>
+      <c r="H115" s="5"/>
+      <c r="I115" s="5"/>
+      <c r="J115" s="5"/>
+      <c r="K115" s="5"/>
+      <c r="L115" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="M112" s="5"/>
-      <c r="N112" s="5"/>
-      <c r="O112" s="5"/>
-      <c r="P112" s="5"/>
-    </row>
-    <row r="113" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B113" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C113" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D113" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="E113" s="4"/>
-      <c r="F113" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="G113" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="H113" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="I113" s="4"/>
-      <c r="J113" s="4"/>
-      <c r="K113" s="4"/>
-      <c r="L113" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="M113" s="4"/>
-      <c r="N113" s="4"/>
-      <c r="O113" s="4"/>
-      <c r="P113" s="4"/>
-    </row>
-    <row r="114" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B114" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C114" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="D114" s="4" t="s">
+      <c r="M115" s="5"/>
+      <c r="N115" s="5"/>
+      <c r="O115" s="5"/>
+      <c r="P115" s="5"/>
+    </row>
+    <row r="116" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B116" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D116" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="E114" s="5"/>
-      <c r="F114" s="5"/>
-      <c r="G114" s="5"/>
-      <c r="H114" s="5"/>
-      <c r="I114" s="5"/>
-      <c r="J114" s="5"/>
-      <c r="K114" s="5"/>
-      <c r="L114" s="5" t="s">
+      <c r="E116" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="F116" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="G116" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="H116" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="I116" s="4"/>
+      <c r="J116" s="4"/>
+      <c r="K116" s="4"/>
+      <c r="L116" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="M116" s="4"/>
+      <c r="N116" s="4"/>
+      <c r="O116" s="4"/>
+      <c r="P116" s="4"/>
+    </row>
+    <row r="117" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B117" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C117" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="D117" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E117" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="F117" s="5"/>
+      <c r="G117" s="5"/>
+      <c r="H117" s="5"/>
+      <c r="I117" s="5"/>
+      <c r="J117" s="5"/>
+      <c r="K117" s="5"/>
+      <c r="L117" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="M114" s="5"/>
-      <c r="N114" s="5"/>
-      <c r="O114" s="5"/>
-      <c r="P114" s="5"/>
-    </row>
-    <row r="115" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B115" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C115" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D115" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="E115" s="4"/>
-      <c r="F115" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="G115" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="H115" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="I115" s="4"/>
-      <c r="J115" s="4"/>
-      <c r="K115" s="4"/>
-      <c r="L115" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="M115" s="4"/>
-      <c r="N115" s="4"/>
-      <c r="O115" s="4"/>
-      <c r="P115" s="4"/>
-    </row>
-    <row r="116" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B116" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C116" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="D116" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="E116" s="5"/>
-      <c r="F116" s="5"/>
-      <c r="G116" s="5"/>
-      <c r="H116" s="5"/>
-      <c r="I116" s="5"/>
-      <c r="J116" s="5"/>
-      <c r="K116" s="5"/>
-      <c r="L116" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M116" s="5"/>
-      <c r="N116" s="5"/>
-      <c r="O116" s="5"/>
-      <c r="P116" s="5"/>
-    </row>
-    <row r="117" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B117" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C117" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D117" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="E117" s="4"/>
-      <c r="F117" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="G117" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="H117" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="I117" s="4"/>
-      <c r="J117" s="4"/>
-      <c r="K117" s="4"/>
-      <c r="L117" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="M117" s="4"/>
-      <c r="N117" s="4"/>
-      <c r="O117" s="4"/>
-      <c r="P117" s="4"/>
+      <c r="M117" s="5"/>
+      <c r="N117" s="5"/>
+      <c r="O117" s="5"/>
+      <c r="P117" s="5"/>
     </row>
     <row r="118" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B118" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C118" s="5" t="s">
-        <v>24</v>
+      <c r="C118" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E118" s="4"/>
+        <v>200</v>
+      </c>
+      <c r="E118" s="8" t="s">
+        <v>300</v>
+      </c>
       <c r="F118" s="5" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="G118" s="5" t="s">
-        <v>22</v>
+        <v>150</v>
       </c>
       <c r="H118" s="5" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="I118" s="4"/>
       <c r="J118" s="4"/>
       <c r="K118" s="4"/>
       <c r="L118" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M118" s="4"/>
       <c r="N118" s="4"/>
@@ -4849,27 +5363,29 @@
       <c r="B119" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C119" s="4" t="s">
-        <v>47</v>
+      <c r="C119" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E119" s="4"/>
+        <v>108</v>
+      </c>
+      <c r="E119" s="8" t="s">
+        <v>301</v>
+      </c>
       <c r="F119" s="5" t="s">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="G119" s="5" t="s">
-        <v>151</v>
+        <v>22</v>
       </c>
       <c r="H119" s="5" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="I119" s="4"/>
       <c r="J119" s="4"/>
       <c r="K119" s="4"/>
       <c r="L119" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M119" s="4"/>
       <c r="N119" s="4"/>
@@ -4880,27 +5396,29 @@
       <c r="B120" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C120" s="5" t="s">
-        <v>24</v>
+      <c r="C120" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E120" s="4"/>
+        <v>109</v>
+      </c>
+      <c r="E120" s="8" t="s">
+        <v>302</v>
+      </c>
       <c r="F120" s="5" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="G120" s="5" t="s">
-        <v>22</v>
+        <v>150</v>
       </c>
       <c r="H120" s="5" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="I120" s="4"/>
       <c r="J120" s="4"/>
       <c r="K120" s="4"/>
       <c r="L120" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M120" s="4"/>
       <c r="N120" s="4"/>
@@ -4908,86 +5426,92 @@
       <c r="P120" s="4"/>
     </row>
     <row r="121" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B121" s="6" t="s">
+      <c r="B121" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>196</v>
+        <v>24</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="E121" s="5"/>
-      <c r="F121" s="5"/>
-      <c r="G121" s="5"/>
-      <c r="H121" s="5"/>
-      <c r="I121" s="5"/>
-      <c r="J121" s="5"/>
-      <c r="K121" s="5"/>
-      <c r="L121" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E121" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="F121" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="G121" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H121" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="I121" s="4"/>
+      <c r="J121" s="4"/>
+      <c r="K121" s="4"/>
+      <c r="L121" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="M121" s="4"/>
+      <c r="N121" s="4"/>
+      <c r="O121" s="4"/>
+      <c r="P121" s="4"/>
+    </row>
+    <row r="122" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B122" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C122" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="D122" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="E122" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="F122" s="5"/>
+      <c r="G122" s="5"/>
+      <c r="H122" s="5"/>
+      <c r="I122" s="5"/>
+      <c r="J122" s="5"/>
+      <c r="K122" s="5"/>
+      <c r="L122" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="M121" s="5"/>
-      <c r="N121" s="5"/>
-      <c r="O121" s="5"/>
-      <c r="P121" s="5"/>
-    </row>
-    <row r="122" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B122" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C122" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D122" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="E122" s="4"/>
-      <c r="F122" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="G122" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H122" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="I122" s="4"/>
-      <c r="J122" s="4"/>
-      <c r="K122" s="4"/>
-      <c r="L122" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="M122" s="4"/>
-      <c r="N122" s="4"/>
-      <c r="O122" s="4"/>
-      <c r="P122" s="4"/>
+      <c r="M122" s="5"/>
+      <c r="N122" s="5"/>
+      <c r="O122" s="5"/>
+      <c r="P122" s="5"/>
     </row>
     <row r="123" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B123" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C123" s="4" t="s">
-        <v>47</v>
+      <c r="C123" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="E123" s="4"/>
+        <v>111</v>
+      </c>
+      <c r="E123" s="8" t="s">
+        <v>305</v>
+      </c>
       <c r="F123" s="5" t="s">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="G123" s="5" t="s">
-        <v>151</v>
+        <v>22</v>
       </c>
       <c r="H123" s="5" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="I123" s="4"/>
       <c r="J123" s="4"/>
       <c r="K123" s="4"/>
       <c r="L123" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M123" s="4"/>
       <c r="N123" s="4"/>
@@ -4998,27 +5522,29 @@
       <c r="B124" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C124" s="5" t="s">
-        <v>24</v>
+      <c r="C124" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="E124" s="4"/>
+        <v>112</v>
+      </c>
+      <c r="E124" s="8" t="s">
+        <v>306</v>
+      </c>
       <c r="F124" s="5" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="G124" s="5" t="s">
-        <v>22</v>
+        <v>150</v>
       </c>
       <c r="H124" s="5" t="s">
-        <v>159</v>
+        <v>203</v>
       </c>
       <c r="I124" s="4"/>
       <c r="J124" s="4"/>
       <c r="K124" s="4"/>
       <c r="L124" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M124" s="4"/>
       <c r="N124" s="4"/>
@@ -5029,27 +5555,29 @@
       <c r="B125" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C125" s="4" t="s">
-        <v>47</v>
+      <c r="C125" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="E125" s="4"/>
+        <v>113</v>
+      </c>
+      <c r="E125" s="8" t="s">
+        <v>307</v>
+      </c>
       <c r="F125" s="5" t="s">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="G125" s="5" t="s">
-        <v>151</v>
+        <v>22</v>
       </c>
       <c r="H125" s="5" t="s">
-        <v>183</v>
+        <v>156</v>
       </c>
       <c r="I125" s="4"/>
       <c r="J125" s="4"/>
       <c r="K125" s="4"/>
       <c r="L125" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M125" s="4"/>
       <c r="N125" s="4"/>
@@ -5060,27 +5588,29 @@
       <c r="B126" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C126" s="5" t="s">
-        <v>24</v>
+      <c r="C126" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="E126" s="4"/>
+        <v>114</v>
+      </c>
+      <c r="E126" s="8" t="s">
+        <v>308</v>
+      </c>
       <c r="F126" s="5" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="G126" s="5" t="s">
-        <v>22</v>
+        <v>150</v>
       </c>
       <c r="H126" s="5" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="I126" s="4"/>
       <c r="J126" s="4"/>
       <c r="K126" s="4"/>
       <c r="L126" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M126" s="4"/>
       <c r="N126" s="4"/>
@@ -5091,27 +5621,29 @@
       <c r="B127" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C127" s="4" t="s">
-        <v>47</v>
+      <c r="C127" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="E127" s="4"/>
+        <v>115</v>
+      </c>
+      <c r="E127" s="8" t="s">
+        <v>309</v>
+      </c>
       <c r="F127" s="5" t="s">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="G127" s="5" t="s">
-        <v>151</v>
+        <v>22</v>
       </c>
       <c r="H127" s="5" t="s">
-        <v>201</v>
+        <v>158</v>
       </c>
       <c r="I127" s="4"/>
       <c r="J127" s="4"/>
       <c r="K127" s="4"/>
       <c r="L127" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M127" s="4"/>
       <c r="N127" s="4"/>
@@ -5122,27 +5654,29 @@
       <c r="B128" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C128" s="5" t="s">
-        <v>24</v>
+      <c r="C128" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="E128" s="4"/>
+        <v>116</v>
+      </c>
+      <c r="E128" s="8" t="s">
+        <v>310</v>
+      </c>
       <c r="F128" s="5" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="G128" s="5" t="s">
-        <v>22</v>
+        <v>150</v>
       </c>
       <c r="H128" s="5" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="I128" s="4"/>
       <c r="J128" s="4"/>
       <c r="K128" s="4"/>
       <c r="L128" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M128" s="4"/>
       <c r="N128" s="4"/>
@@ -5151,35 +5685,49 @@
     </row>
     <row r="129" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B129" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="C129" s="5"/>
-      <c r="D129" s="7"/>
-      <c r="E129" s="8"/>
+        <v>21</v>
+      </c>
+      <c r="C129" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D129" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E129" s="8" t="s">
+        <v>311</v>
+      </c>
       <c r="F129" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="G129" s="5"/>
-      <c r="H129" s="5"/>
-      <c r="I129" s="7"/>
-      <c r="J129" s="7"/>
-      <c r="K129" s="7"/>
-      <c r="L129" s="7"/>
-      <c r="M129" s="7"/>
-      <c r="N129" s="7"/>
-      <c r="O129" s="7"/>
-      <c r="P129" s="7"/>
+        <v>135</v>
+      </c>
+      <c r="G129" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H129" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="I129" s="4"/>
+      <c r="J129" s="4"/>
+      <c r="K129" s="4"/>
+      <c r="L129" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="M129" s="4"/>
+      <c r="N129" s="4"/>
+      <c r="O129" s="4"/>
+      <c r="P129" s="4"/>
     </row>
     <row r="130" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B130" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="C130" s="4"/>
+      <c r="B130" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C130" s="5"/>
       <c r="D130" s="4"/>
-      <c r="E130" s="4"/>
-      <c r="F130" s="4"/>
-      <c r="G130" s="4"/>
-      <c r="H130" s="4"/>
+      <c r="E130" s="8"/>
+      <c r="F130" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="G130" s="5"/>
+      <c r="H130" s="5"/>
       <c r="I130" s="4"/>
       <c r="J130" s="4"/>
       <c r="K130" s="4"/>
@@ -5187,193 +5735,187 @@
       <c r="M130" s="4"/>
       <c r="N130" s="4"/>
       <c r="O130" s="4"/>
-      <c r="P130" s="4" t="s">
-        <v>156</v>
-      </c>
+      <c r="P130" s="4"/>
     </row>
     <row r="131" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B131" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C131" s="6"/>
-      <c r="D131" s="6"/>
-      <c r="E131" s="6"/>
-      <c r="F131" s="6"/>
-      <c r="G131" s="6"/>
-      <c r="H131" s="6"/>
-      <c r="I131" s="6"/>
-      <c r="J131" s="6"/>
-      <c r="K131" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L131" s="6"/>
-      <c r="M131" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="N131" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="O131" s="6"/>
-      <c r="P131" s="6"/>
+      <c r="B131" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C131" s="4"/>
+      <c r="D131" s="4"/>
+      <c r="E131" s="8"/>
+      <c r="F131" s="4"/>
+      <c r="G131" s="4"/>
+      <c r="H131" s="4"/>
+      <c r="I131" s="4"/>
+      <c r="J131" s="4"/>
+      <c r="K131" s="4"/>
+      <c r="L131" s="4"/>
+      <c r="M131" s="4"/>
+      <c r="N131" s="4"/>
+      <c r="O131" s="4"/>
+      <c r="P131" s="4" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="132" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B132" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="6"/>
-      <c r="E132" s="6"/>
+      <c r="E132" s="8"/>
       <c r="F132" s="6"/>
       <c r="G132" s="6"/>
       <c r="H132" s="6"/>
       <c r="I132" s="6"/>
       <c r="J132" s="6"/>
       <c r="K132" s="6" t="s">
-        <v>193</v>
+        <v>23</v>
       </c>
       <c r="L132" s="6"/>
-      <c r="M132" s="6"/>
-      <c r="N132" s="6"/>
+      <c r="M132" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="N132" s="6" t="s">
+        <v>23</v>
+      </c>
       <c r="O132" s="6"/>
       <c r="P132" s="6"/>
     </row>
     <row r="133" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B133" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C133" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D133" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="E133" s="5"/>
-      <c r="F133" s="5"/>
-      <c r="G133" s="5"/>
-      <c r="H133" s="5"/>
-      <c r="I133" s="5"/>
-      <c r="J133" s="5"/>
-      <c r="K133" s="5"/>
-      <c r="L133" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M133" s="5"/>
-      <c r="N133" s="5"/>
-      <c r="O133" s="5"/>
-      <c r="P133" s="5"/>
+        <v>148</v>
+      </c>
+      <c r="C133" s="6"/>
+      <c r="D133" s="6"/>
+      <c r="E133" s="8"/>
+      <c r="F133" s="6"/>
+      <c r="G133" s="6"/>
+      <c r="H133" s="6"/>
+      <c r="I133" s="6"/>
+      <c r="J133" s="6"/>
+      <c r="K133" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="L133" s="6"/>
+      <c r="M133" s="6"/>
+      <c r="N133" s="6"/>
+      <c r="O133" s="6"/>
+      <c r="P133" s="6"/>
     </row>
     <row r="134" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B134" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C134" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D134" s="4" t="s">
-        <v>120</v>
-      </c>
+      <c r="B134" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C134" s="4"/>
+      <c r="D134" s="4"/>
       <c r="E134" s="4"/>
-      <c r="F134" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="G134" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="H134" s="5" t="s">
-        <v>190</v>
-      </c>
+      <c r="F134" s="4"/>
+      <c r="G134" s="4"/>
+      <c r="H134" s="4"/>
       <c r="I134" s="4"/>
-      <c r="J134" s="4"/>
+      <c r="J134" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="K134" s="4"/>
-      <c r="L134" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="M134" s="4"/>
-      <c r="N134" s="4"/>
+      <c r="L134" s="4"/>
+      <c r="M134" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="N134" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="O134" s="4"/>
       <c r="P134" s="4"/>
     </row>
     <row r="135" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B135" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C135" s="4" t="s">
-        <v>47</v>
+      <c r="B135" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C135" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="E135" s="4"/>
-      <c r="F135" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="G135" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="H135" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="I135" s="4"/>
-      <c r="J135" s="4"/>
-      <c r="K135" s="4"/>
-      <c r="L135" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="M135" s="4"/>
-      <c r="N135" s="4"/>
-      <c r="O135" s="4"/>
-      <c r="P135" s="4"/>
+        <v>118</v>
+      </c>
+      <c r="E135" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="F135" s="5"/>
+      <c r="G135" s="5"/>
+      <c r="H135" s="5"/>
+      <c r="I135" s="5"/>
+      <c r="J135" s="5"/>
+      <c r="K135" s="5"/>
+      <c r="L135" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M135" s="5"/>
+      <c r="N135" s="5"/>
+      <c r="O135" s="5"/>
+      <c r="P135" s="5"/>
     </row>
     <row r="136" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B136" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C136" s="5" t="s">
-        <v>25</v>
+      <c r="B136" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C136" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="E136" s="5"/>
-      <c r="F136" s="5"/>
-      <c r="G136" s="5"/>
-      <c r="H136" s="5"/>
-      <c r="I136" s="5"/>
-      <c r="J136" s="5"/>
-      <c r="K136" s="5"/>
-      <c r="L136" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M136" s="5"/>
-      <c r="N136" s="5"/>
-      <c r="O136" s="5"/>
-      <c r="P136" s="5"/>
+        <v>119</v>
+      </c>
+      <c r="E136" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="F136" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="G136" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="H136" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="I136" s="4"/>
+      <c r="J136" s="4"/>
+      <c r="K136" s="4"/>
+      <c r="L136" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="M136" s="4"/>
+      <c r="N136" s="4"/>
+      <c r="O136" s="4"/>
+      <c r="P136" s="4"/>
     </row>
     <row r="137" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B137" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="E137" s="4"/>
+        <v>120</v>
+      </c>
+      <c r="E137" s="8" t="s">
+        <v>314</v>
+      </c>
       <c r="F137" s="5" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G137" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H137" s="5" t="s">
-        <v>168</v>
+        <v>205</v>
       </c>
       <c r="I137" s="4"/>
       <c r="J137" s="4"/>
       <c r="K137" s="4"/>
       <c r="L137" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M137" s="4"/>
       <c r="N137" s="4"/>
@@ -5388,9 +5930,11 @@
         <v>25</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="E138" s="5"/>
+        <v>121</v>
+      </c>
+      <c r="E138" s="8" t="s">
+        <v>315</v>
+      </c>
       <c r="F138" s="5"/>
       <c r="G138" s="5"/>
       <c r="H138" s="5"/>
@@ -5410,26 +5954,34 @@
         <v>21</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="E139" s="4"/>
+        <v>122</v>
+      </c>
+      <c r="E139" s="8" t="s">
+        <v>316</v>
+      </c>
       <c r="F139" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="G139" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="H139" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="G139" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="H139" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="I139" s="4"/>
-      <c r="J139" s="4"/>
-      <c r="K139" s="4"/>
+      <c r="I139" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="J139" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="K139" s="4" t="s">
+        <v>331</v>
+      </c>
       <c r="L139" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M139" s="4"/>
       <c r="N139" s="4"/>
@@ -5437,61 +5989,59 @@
       <c r="P139" s="4"/>
     </row>
     <row r="140" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B140" s="5" t="s">
+      <c r="B140" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E140" s="4"/>
-      <c r="F140" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="G140" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H140" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="I140" s="4"/>
-      <c r="J140" s="4"/>
-      <c r="K140" s="4"/>
-      <c r="L140" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="M140" s="4"/>
-      <c r="N140" s="4"/>
-      <c r="O140" s="4"/>
-      <c r="P140" s="4"/>
+        <v>123</v>
+      </c>
+      <c r="E140" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="F140" s="5"/>
+      <c r="G140" s="5"/>
+      <c r="H140" s="5"/>
+      <c r="I140" s="5"/>
+      <c r="J140" s="5"/>
+      <c r="K140" s="5"/>
+      <c r="L140" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M140" s="5"/>
+      <c r="N140" s="5"/>
+      <c r="O140" s="5"/>
+      <c r="P140" s="5"/>
     </row>
     <row r="141" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B141" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="E141" s="4"/>
+        <v>124</v>
+      </c>
+      <c r="E141" s="8" t="s">
+        <v>318</v>
+      </c>
       <c r="F141" s="5" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G141" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H141" s="5" t="s">
-        <v>183</v>
+        <v>206</v>
       </c>
       <c r="I141" s="4"/>
       <c r="J141" s="4"/>
       <c r="K141" s="4"/>
       <c r="L141" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M141" s="4"/>
       <c r="N141" s="4"/>
@@ -5500,156 +6050,166 @@
     </row>
     <row r="142" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B142" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="C142" s="5"/>
-      <c r="D142" s="7"/>
-      <c r="E142" s="8"/>
-      <c r="F142" s="5"/>
-      <c r="G142" s="5"/>
-      <c r="H142" s="5"/>
-      <c r="I142" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="J142" s="7"/>
-      <c r="K142" s="7"/>
-      <c r="L142" s="7"/>
-      <c r="M142" s="7"/>
-      <c r="N142" s="7"/>
-      <c r="O142" s="7"/>
-      <c r="P142" s="7"/>
+        <v>21</v>
+      </c>
+      <c r="C142" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D142" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="E142" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="F142" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="G142" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H142" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="I142" s="4"/>
+      <c r="J142" s="4"/>
+      <c r="K142" s="4"/>
+      <c r="L142" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="M142" s="4"/>
+      <c r="N142" s="4"/>
+      <c r="O142" s="4"/>
+      <c r="P142" s="4"/>
     </row>
     <row r="143" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B143" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C143" s="4"/>
-      <c r="D143" s="4"/>
-      <c r="E143" s="4"/>
-      <c r="F143" s="4"/>
-      <c r="G143" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="H143" s="4"/>
-      <c r="I143" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="J143" s="4" t="s">
-        <v>146</v>
-      </c>
+      <c r="B143" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C143" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D143" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E143" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="F143" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="G143" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="H143" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="I143" s="4"/>
+      <c r="J143" s="4"/>
       <c r="K143" s="4"/>
-      <c r="L143" s="4"/>
+      <c r="L143" s="4" t="s">
+        <v>138</v>
+      </c>
       <c r="M143" s="4"/>
       <c r="N143" s="4"/>
       <c r="O143" s="4"/>
-      <c r="P143" s="4" t="s">
+      <c r="P143" s="4"/>
+    </row>
+    <row r="144" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B144" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="C144" s="5"/>
+      <c r="D144" s="4"/>
+      <c r="E144" s="8"/>
+      <c r="F144" s="5"/>
+      <c r="G144" s="5"/>
+      <c r="H144" s="5"/>
+      <c r="I144" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="J144" s="4"/>
+      <c r="K144" s="4"/>
+      <c r="L144" s="4"/>
+      <c r="M144" s="4"/>
+      <c r="N144" s="4"/>
+      <c r="O144" s="4"/>
+      <c r="P144" s="4"/>
+    </row>
+    <row r="145" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B145" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C145" s="4"/>
+      <c r="D145" s="4"/>
+      <c r="E145" s="8"/>
+      <c r="F145" s="4"/>
+      <c r="G145" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="H145" s="4"/>
+      <c r="I145" s="4" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="144" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B144" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C144" s="6"/>
-      <c r="D144" s="6"/>
-      <c r="E144" s="6"/>
-      <c r="F144" s="6"/>
-      <c r="G144" s="6"/>
-      <c r="H144" s="6"/>
-      <c r="I144" s="6"/>
-      <c r="J144" s="6"/>
-      <c r="K144" s="6"/>
-      <c r="L144" s="6"/>
-      <c r="M144" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="N144" s="6"/>
-      <c r="O144" s="6"/>
-      <c r="P144" s="6"/>
-    </row>
-    <row r="145" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B145" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C145" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="D145" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="E145" s="4"/>
-      <c r="F145" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="G145" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="H145" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="I145" s="4"/>
-      <c r="J145" s="4"/>
+      <c r="J145" s="4" t="s">
+        <v>145</v>
+      </c>
       <c r="K145" s="4"/>
-      <c r="L145" s="4" t="s">
-        <v>139</v>
-      </c>
+      <c r="L145" s="4"/>
       <c r="M145" s="4"/>
       <c r="N145" s="4"/>
       <c r="O145" s="4"/>
-      <c r="P145" s="4"/>
+      <c r="P145" s="4" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="146" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B146" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C146" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="D146" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="E146" s="4"/>
-      <c r="F146" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="G146" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="H146" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="I146" s="4"/>
-      <c r="J146" s="4"/>
-      <c r="K146" s="4"/>
-      <c r="L146" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="M146" s="4"/>
-      <c r="N146" s="4"/>
-      <c r="O146" s="4"/>
-      <c r="P146" s="4"/>
+      <c r="B146" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C146" s="6"/>
+      <c r="D146" s="6"/>
+      <c r="E146" s="8"/>
+      <c r="F146" s="6"/>
+      <c r="G146" s="6"/>
+      <c r="H146" s="6"/>
+      <c r="I146" s="6"/>
+      <c r="J146" s="6"/>
+      <c r="K146" s="6"/>
+      <c r="L146" s="6"/>
+      <c r="M146" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="N146" s="6"/>
+      <c r="O146" s="6"/>
+      <c r="P146" s="6"/>
     </row>
     <row r="147" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B147" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>47</v>
+        <v>127</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="E147" s="4"/>
-      <c r="F147" s="5"/>
-      <c r="G147" s="5"/>
+        <v>128</v>
+      </c>
+      <c r="E147" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="F147" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="G147" s="5" t="s">
+        <v>150</v>
+      </c>
       <c r="H147" s="5" t="s">
-        <v>215</v>
+        <v>155</v>
       </c>
       <c r="I147" s="4"/>
       <c r="J147" s="4"/>
       <c r="K147" s="4"/>
       <c r="L147" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M147" s="4"/>
       <c r="N147" s="4"/>
@@ -5657,55 +6217,65 @@
       <c r="P147" s="4"/>
     </row>
     <row r="148" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B148" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C148" s="5" t="s">
-        <v>25</v>
+      <c r="B148" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C148" s="4" t="s">
+        <v>127</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="E148" s="5"/>
-      <c r="F148" s="5"/>
-      <c r="G148" s="5"/>
-      <c r="H148" s="5"/>
-      <c r="I148" s="5"/>
-      <c r="J148" s="5"/>
-      <c r="K148" s="5"/>
-      <c r="L148" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M148" s="5"/>
-      <c r="N148" s="5"/>
-      <c r="O148" s="5"/>
-      <c r="P148" s="5"/>
+        <v>129</v>
+      </c>
+      <c r="E148" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="F148" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="G148" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="H148" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="I148" s="4"/>
+      <c r="J148" s="4"/>
+      <c r="K148" s="4"/>
+      <c r="L148" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="M148" s="4"/>
+      <c r="N148" s="4"/>
+      <c r="O148" s="4"/>
+      <c r="P148" s="4"/>
     </row>
     <row r="149" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B149" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>128</v>
+        <v>46</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="E149" s="4"/>
-      <c r="F149" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="E149" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="F149" s="5"/>
+      <c r="G149" s="5"/>
+      <c r="H149" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="G149" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="H149" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="I149" s="4"/>
-      <c r="J149" s="4"/>
+      <c r="I149" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="J149" s="4" t="s">
+        <v>138</v>
+      </c>
       <c r="K149" s="4"/>
       <c r="L149" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M149" s="4"/>
       <c r="N149" s="4"/>
@@ -5713,123 +6283,135 @@
       <c r="P149" s="4"/>
     </row>
     <row r="150" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B150" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="C150" s="7"/>
-      <c r="D150" s="7"/>
-      <c r="E150" s="8"/>
-      <c r="F150" s="5" t="s">
-        <v>211</v>
-      </c>
+      <c r="B150" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C150" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D150" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="E150" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="F150" s="5"/>
       <c r="G150" s="5"/>
       <c r="H150" s="5"/>
-      <c r="I150" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="J150" s="7"/>
-      <c r="K150" s="7"/>
-      <c r="L150" s="7"/>
-      <c r="M150" s="7"/>
-      <c r="N150" s="7"/>
-      <c r="O150" s="7"/>
-      <c r="P150" s="7"/>
+      <c r="I150" s="5"/>
+      <c r="J150" s="5"/>
+      <c r="K150" s="5"/>
+      <c r="L150" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M150" s="5"/>
+      <c r="N150" s="5"/>
+      <c r="O150" s="5"/>
+      <c r="P150" s="5"/>
     </row>
     <row r="151" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B151" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C151" s="6"/>
-      <c r="D151" s="6"/>
-      <c r="E151" s="6"/>
-      <c r="F151" s="6"/>
-      <c r="G151" s="6"/>
-      <c r="H151" s="6"/>
-      <c r="I151" s="6"/>
-      <c r="J151" s="6"/>
-      <c r="K151" s="6"/>
-      <c r="L151" s="6"/>
-      <c r="M151" s="6" t="s">
+      <c r="B151" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C151" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="D151" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E151" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="F151" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="G151" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="H151" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="N151" s="6"/>
-      <c r="O151" s="6"/>
-      <c r="P151" s="6"/>
+      <c r="I151" s="4"/>
+      <c r="J151" s="4"/>
+      <c r="K151" s="4"/>
+      <c r="L151" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="M151" s="4"/>
+      <c r="N151" s="4"/>
+      <c r="O151" s="4"/>
+      <c r="P151" s="4"/>
     </row>
     <row r="152" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B152" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C152" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D152" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="E152" s="5"/>
-      <c r="F152" s="5"/>
+      <c r="B152" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C152" s="4"/>
+      <c r="D152" s="4"/>
+      <c r="E152" s="8"/>
+      <c r="F152" s="5" t="s">
+        <v>207</v>
+      </c>
       <c r="G152" s="5"/>
       <c r="H152" s="5"/>
-      <c r="I152" s="5"/>
-      <c r="J152" s="5"/>
-      <c r="K152" s="5"/>
-      <c r="L152" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M152" s="5"/>
-      <c r="N152" s="5"/>
-      <c r="O152" s="5"/>
-      <c r="P152" s="5"/>
+      <c r="I152" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="J152" s="4"/>
+      <c r="K152" s="4"/>
+      <c r="L152" s="4"/>
+      <c r="M152" s="4"/>
+      <c r="N152" s="4"/>
+      <c r="O152" s="4"/>
+      <c r="P152" s="4"/>
     </row>
     <row r="153" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B153" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C153" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D153" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="E153" s="4"/>
-      <c r="F153" s="5"/>
-      <c r="G153" s="5"/>
-      <c r="H153" s="5"/>
-      <c r="I153" s="4"/>
-      <c r="J153" s="4"/>
-      <c r="K153" s="4"/>
-      <c r="L153" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="M153" s="4"/>
-      <c r="N153" s="4"/>
-      <c r="O153" s="4"/>
-      <c r="P153" s="4"/>
+      <c r="B153" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C153" s="6"/>
+      <c r="D153" s="6"/>
+      <c r="E153" s="8"/>
+      <c r="F153" s="6"/>
+      <c r="G153" s="6"/>
+      <c r="H153" s="6"/>
+      <c r="I153" s="6"/>
+      <c r="J153" s="6"/>
+      <c r="K153" s="6"/>
+      <c r="L153" s="6"/>
+      <c r="M153" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="N153" s="6"/>
+      <c r="O153" s="6"/>
+      <c r="P153" s="6"/>
     </row>
     <row r="154" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B154" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C154" s="4" t="s">
-        <v>47</v>
+      <c r="B154" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C154" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="E154" s="4"/>
+        <v>131</v>
+      </c>
+      <c r="E154" s="8" t="s">
+        <v>326</v>
+      </c>
       <c r="F154" s="5"/>
       <c r="G154" s="5"/>
       <c r="H154" s="5"/>
-      <c r="I154" s="4"/>
-      <c r="J154" s="4"/>
-      <c r="K154" s="4"/>
-      <c r="L154" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="M154" s="4"/>
-      <c r="N154" s="4"/>
-      <c r="O154" s="4"/>
-      <c r="P154" s="4"/>
+      <c r="I154" s="5"/>
+      <c r="J154" s="5"/>
+      <c r="K154" s="5"/>
+      <c r="L154" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M154" s="5"/>
+      <c r="N154" s="5"/>
+      <c r="O154" s="5"/>
+      <c r="P154" s="5"/>
     </row>
     <row r="155" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B155" s="5" t="s">
@@ -5839,9 +6421,11 @@
         <v>24</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="E155" s="4"/>
+        <v>132</v>
+      </c>
+      <c r="E155" s="8" t="s">
+        <v>327</v>
+      </c>
       <c r="F155" s="5"/>
       <c r="G155" s="5"/>
       <c r="H155" s="5"/>
@@ -5849,7 +6433,7 @@
       <c r="J155" s="4"/>
       <c r="K155" s="4"/>
       <c r="L155" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M155" s="4"/>
       <c r="N155" s="4"/>
@@ -5860,13 +6444,15 @@
       <c r="B156" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C156" s="5" t="s">
-        <v>24</v>
+      <c r="C156" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="E156" s="4"/>
+        <v>209</v>
+      </c>
+      <c r="E156" s="8" t="s">
+        <v>328</v>
+      </c>
       <c r="F156" s="5"/>
       <c r="G156" s="5"/>
       <c r="H156" s="5"/>
@@ -5874,7 +6460,7 @@
       <c r="J156" s="4"/>
       <c r="K156" s="4"/>
       <c r="L156" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M156" s="4"/>
       <c r="N156" s="4"/>
@@ -5883,24 +6469,146 @@
     </row>
     <row r="157" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B157" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="C157" s="5"/>
-      <c r="D157" s="7"/>
-      <c r="E157" s="8"/>
+        <v>21</v>
+      </c>
+      <c r="C157" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D157" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E157" s="8" t="s">
+        <v>329</v>
+      </c>
       <c r="F157" s="5"/>
       <c r="G157" s="5"/>
       <c r="H157" s="5"/>
-      <c r="I157" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="J157" s="7"/>
-      <c r="K157" s="7"/>
-      <c r="L157" s="7"/>
-      <c r="M157" s="7"/>
-      <c r="N157" s="7"/>
-      <c r="O157" s="7"/>
-      <c r="P157" s="7"/>
+      <c r="I157" s="4"/>
+      <c r="J157" s="4"/>
+      <c r="K157" s="4"/>
+      <c r="L157" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="M157" s="4"/>
+      <c r="N157" s="4"/>
+      <c r="O157" s="4"/>
+      <c r="P157" s="4"/>
+    </row>
+    <row r="158" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B158" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C158" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D158" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E158" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="F158" s="5"/>
+      <c r="G158" s="5"/>
+      <c r="H158" s="5"/>
+      <c r="I158" s="4"/>
+      <c r="J158" s="4"/>
+      <c r="K158" s="4"/>
+      <c r="L158" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="M158" s="4"/>
+      <c r="N158" s="4"/>
+      <c r="O158" s="4"/>
+      <c r="P158" s="4"/>
+    </row>
+    <row r="159" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B159" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="C159" s="5"/>
+      <c r="D159" s="4"/>
+      <c r="E159" s="8"/>
+      <c r="F159" s="5"/>
+      <c r="G159" s="5"/>
+      <c r="H159" s="5"/>
+      <c r="I159" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="J159" s="4"/>
+      <c r="K159" s="4"/>
+      <c r="L159" s="4"/>
+      <c r="M159" s="4"/>
+      <c r="N159" s="4"/>
+      <c r="O159" s="4"/>
+      <c r="P159" s="4"/>
+    </row>
+    <row r="160" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B160" s="9"/>
+      <c r="C160" s="9"/>
+      <c r="D160" s="9"/>
+      <c r="E160" s="8"/>
+      <c r="F160" s="9"/>
+      <c r="G160" s="9"/>
+      <c r="H160" s="9"/>
+      <c r="I160" s="9"/>
+      <c r="J160" s="9"/>
+      <c r="K160" s="9"/>
+      <c r="L160" s="9"/>
+      <c r="M160" s="9"/>
+      <c r="N160" s="9"/>
+      <c r="O160" s="9"/>
+      <c r="P160" s="9"/>
+    </row>
+    <row r="161" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B161" s="9"/>
+      <c r="C161" s="9"/>
+      <c r="D161" s="9"/>
+      <c r="E161" s="8"/>
+      <c r="F161" s="9"/>
+      <c r="G161" s="9"/>
+      <c r="H161" s="9"/>
+      <c r="I161" s="9"/>
+      <c r="J161" s="9"/>
+      <c r="K161" s="9"/>
+      <c r="L161" s="9"/>
+      <c r="M161" s="9"/>
+      <c r="N161" s="9"/>
+      <c r="O161" s="9"/>
+      <c r="P161" s="9"/>
+    </row>
+    <row r="162" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B162" s="9"/>
+      <c r="C162" s="9"/>
+      <c r="D162" s="9"/>
+      <c r="E162" s="8"/>
+      <c r="F162" s="9"/>
+      <c r="G162" s="9"/>
+      <c r="H162" s="9"/>
+      <c r="I162" s="9"/>
+      <c r="J162" s="9"/>
+      <c r="K162" s="9"/>
+      <c r="L162" s="9"/>
+      <c r="M162" s="9"/>
+      <c r="N162" s="9"/>
+      <c r="O162" s="9"/>
+      <c r="P162" s="9"/>
+    </row>
+    <row r="163" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B163" s="9"/>
+      <c r="C163" s="9"/>
+      <c r="D163" s="9"/>
+      <c r="E163" s="5"/>
+      <c r="F163" s="9"/>
+      <c r="G163" s="9"/>
+      <c r="H163" s="9"/>
+      <c r="I163" s="9"/>
+      <c r="J163" s="9"/>
+      <c r="K163" s="9"/>
+      <c r="L163" s="9"/>
+      <c r="M163" s="9"/>
+      <c r="N163" s="9"/>
+      <c r="O163" s="9"/>
+      <c r="P163" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
